--- a/data/source_papers.xlsx
+++ b/data/source_papers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa77\Documents\.MIJN BESTANDEN\Wiskunde &amp; Informatica\NAS website\GitHub repo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A38629C-4F7A-4032-9DCD-FC4B2B9FC914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468F3714-55F1-4486-9090-6E8A29EE3219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5391,9 +5391,6 @@
     <t>10.1109/tnsm.2025.3607004</t>
   </si>
   <si>
-    <t>X. Liu, R. Kooij, P.V. Mieghem</t>
-  </si>
-  <si>
     <t>Node-Reliability: Monte Carlo, Laplace, and Stochastic Approximations and a Greedy Link-Augmentation Strategy</t>
   </si>
   <si>
@@ -5464,6 +5461,9 @@
   </si>
   <si>
     <t>B.L. Chang, L. Yang, M. Sensi, M.A. Achterberg, F. Wang, M. Rinaldi, P. Van Mieghem</t>
+  </si>
+  <si>
+    <t>X. Liu, R. Kooij, P. Van Mieghem</t>
   </si>
 </sst>
 </file>
@@ -5869,16 +5869,16 @@
     </row>
     <row r="2" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="B2" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="C2">
         <v>2026</v>
       </c>
       <c r="D2" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="F2" t="s">
         <v>750</v>
@@ -5889,19 +5889,19 @@
     </row>
     <row r="3" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="B3" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="C3">
         <v>2026</v>
       </c>
       <c r="D3" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="E3" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="F3" t="s">
         <v>2</v>
@@ -5913,7 +5913,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="J3" t="s">
         <v>1003</v>
@@ -5924,10 +5924,10 @@
     </row>
     <row r="4" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="B4" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="C4">
         <v>2025</v>
@@ -5936,7 +5936,7 @@
         <v>854</v>
       </c>
       <c r="E4" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="F4" t="s">
         <v>2</v>
@@ -5948,7 +5948,7 @@
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="J4" t="s">
         <v>806</v>
@@ -5959,10 +5959,10 @@
     </row>
     <row r="5" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="B5" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="C5">
         <v>2025</v>
@@ -5971,7 +5971,7 @@
         <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="F5" t="s">
         <v>2</v>
@@ -5983,7 +5983,7 @@
         <v>9</v>
       </c>
       <c r="I5" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="J5" t="s">
         <v>903</v>
@@ -5994,10 +5994,10 @@
     </row>
     <row r="6" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B6" t="s">
-        <v>1787</v>
+        <v>1811</v>
       </c>
       <c r="C6">
         <v>2026</v>
@@ -6416,10 +6416,10 @@
     </row>
     <row r="19" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B19" t="s">
         <v>1805</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1806</v>
       </c>
       <c r="C19">
         <v>2024</v>
@@ -6428,7 +6428,7 @@
         <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="F19" t="s">
         <v>2</v>
@@ -6486,7 +6486,7 @@
         <v>2024</v>
       </c>
       <c r="D21" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="F21" t="s">
         <v>750</v>
@@ -6494,7 +6494,7 @@
     </row>
     <row r="22" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="B22" t="s">
         <v>1750</v>
@@ -6503,7 +6503,7 @@
         <v>2024</v>
       </c>
       <c r="D22" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="F22" t="s">
         <v>750</v>
@@ -7987,7 +7987,7 @@
         <v>826</v>
       </c>
       <c r="B68" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="C68">
         <v>2022</v>

--- a/data/source_papers.xlsx
+++ b/data/source_papers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robertogheda\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D6AEF8-EE6B-49BC-AB58-819C75484505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F703F5AF-C8A4-475E-97F3-4F9A5748745B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5550,7 +5550,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5567,17 +5567,24 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5863,7 +5870,7 @@
   <cols>
     <col min="1" max="1" width="63.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="64.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" style="13" customWidth="1"/>
     <col min="4" max="4" width="31.44140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="31" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.6640625" style="1" customWidth="1"/>
@@ -5880,7 +5887,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -5912,76 +5919,76 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>1818</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>1819</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="10">
         <v>2026</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>1820</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>750</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>1814</v>
       </c>
       <c r="B3" t="s">
         <v>1815</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="10">
         <v>2026</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>1816</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
         <v>750</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>1812</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>1817</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <v>2026</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>1813</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
         <v>750</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -5990,7 +5997,7 @@
       <c r="B5" t="s">
         <v>1808</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="11">
         <v>2026</v>
       </c>
       <c r="D5" t="s">
@@ -6010,7 +6017,7 @@
       <c r="B6" t="s">
         <v>1799</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="11">
         <v>2026</v>
       </c>
       <c r="D6" t="s">
@@ -6039,19 +6046,19 @@
       </c>
     </row>
     <row r="7" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>1821</v>
       </c>
       <c r="B7" t="s">
         <v>1822</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="11">
         <v>2025</v>
       </c>
       <c r="D7" t="s">
         <v>1823</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>2</v>
       </c>
     </row>
@@ -6062,7 +6069,7 @@
       <c r="B8" t="s">
         <v>1794</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="11">
         <v>2025</v>
       </c>
       <c r="D8" t="s">
@@ -6097,7 +6104,7 @@
       <c r="B9" t="s">
         <v>1790</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="11">
         <v>2025</v>
       </c>
       <c r="D9" t="s">
@@ -6132,7 +6139,7 @@
       <c r="B10" t="s">
         <v>1811</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="11">
         <v>2026</v>
       </c>
       <c r="D10" t="s">
@@ -6161,7 +6168,7 @@
       <c r="B11" t="s">
         <v>1783</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="11">
         <v>2025</v>
       </c>
       <c r="D11" t="s">
@@ -6193,7 +6200,7 @@
       <c r="B12" t="s">
         <v>1780</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="11">
         <v>2025</v>
       </c>
       <c r="D12" t="s">
@@ -6228,7 +6235,7 @@
       <c r="B13" t="s">
         <v>1776</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="11">
         <v>2025</v>
       </c>
       <c r="D13" t="s">
@@ -6263,7 +6270,7 @@
       <c r="B14" t="s">
         <v>1772</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="11">
         <v>2025</v>
       </c>
       <c r="D14" t="s">
@@ -6295,7 +6302,7 @@
       <c r="B15" t="s">
         <v>1769</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="11">
         <v>2025</v>
       </c>
       <c r="D15" t="s">
@@ -6330,7 +6337,7 @@
       <c r="B16" t="s">
         <v>1764</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="11">
         <v>2024</v>
       </c>
       <c r="D16" t="s">
@@ -6362,7 +6369,7 @@
       <c r="B17" t="s">
         <v>1761</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="11">
         <v>2025</v>
       </c>
       <c r="D17" t="s">
@@ -6394,7 +6401,7 @@
       <c r="B18" t="s">
         <v>1756</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="11">
         <v>2025</v>
       </c>
       <c r="D18" t="s">
@@ -6426,7 +6433,7 @@
       <c r="B19" t="s">
         <v>1753</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="11">
         <v>2025</v>
       </c>
       <c r="D19" t="s">
@@ -6458,7 +6465,7 @@
       <c r="B20" t="s">
         <v>1750</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="11">
         <v>2025</v>
       </c>
       <c r="D20" t="s">
@@ -6493,7 +6500,7 @@
       <c r="B21" t="s">
         <v>1746</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="11">
         <v>2025</v>
       </c>
       <c r="D21" t="s">
@@ -6525,7 +6532,7 @@
       <c r="B22" t="s">
         <v>1741</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="11">
         <v>2025</v>
       </c>
       <c r="D22" t="s">
@@ -6554,7 +6561,7 @@
       <c r="B23" t="s">
         <v>1805</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="11">
         <v>2024</v>
       </c>
       <c r="D23" t="s">
@@ -6583,7 +6590,7 @@
       <c r="B24" t="s">
         <v>458</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="11">
         <v>2024</v>
       </c>
       <c r="D24" t="s">
@@ -6615,7 +6622,7 @@
       <c r="B25" t="s">
         <v>458</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="11">
         <v>2024</v>
       </c>
       <c r="D25" t="s">
@@ -6632,7 +6639,7 @@
       <c r="B26" t="s">
         <v>1750</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="11">
         <v>2024</v>
       </c>
       <c r="D26" t="s">
@@ -6658,7 +6665,7 @@
       <c r="B27" t="s">
         <v>1733</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="11">
         <v>2024</v>
       </c>
       <c r="D27" t="s">
@@ -6690,7 +6697,7 @@
       <c r="B28" t="s">
         <v>770</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="11">
         <v>2024</v>
       </c>
       <c r="D28" t="s">
@@ -6726,7 +6733,7 @@
       <c r="B29" t="s">
         <v>783</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="11">
         <v>2024</v>
       </c>
       <c r="D29" t="s">
@@ -6760,7 +6767,7 @@
       <c r="B30" t="s">
         <v>482</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="11">
         <v>2024</v>
       </c>
       <c r="D30" t="s">
@@ -6796,7 +6803,7 @@
       <c r="B31" t="s">
         <v>789</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="11">
         <v>2024</v>
       </c>
       <c r="D31" t="s">
@@ -6832,7 +6839,7 @@
       <c r="B32" t="s">
         <v>483</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="11">
         <v>2024</v>
       </c>
       <c r="D32" t="s">
@@ -6866,7 +6873,7 @@
       <c r="B33" t="s">
         <v>484</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="11">
         <v>2024</v>
       </c>
       <c r="D33" t="s">
@@ -6892,7 +6899,7 @@
       <c r="B34" t="s">
         <v>485</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="11">
         <v>2024</v>
       </c>
       <c r="D34" t="s">
@@ -6928,7 +6935,7 @@
       <c r="B35" t="s">
         <v>724</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="11">
         <v>2024</v>
       </c>
       <c r="D35" t="s">
@@ -6964,7 +6971,7 @@
       <c r="B36" t="s">
         <v>486</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="11">
         <v>2024</v>
       </c>
       <c r="D36" t="s">
@@ -6996,7 +7003,7 @@
       <c r="B37" t="s">
         <v>492</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="11">
         <v>2024</v>
       </c>
       <c r="D37" t="s">
@@ -7032,7 +7039,7 @@
       <c r="B38" t="s">
         <v>458</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="11">
         <v>2024</v>
       </c>
       <c r="D38" t="s">
@@ -7068,7 +7075,7 @@
       <c r="B39" t="s">
         <v>487</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="11">
         <v>2023</v>
       </c>
       <c r="D39" t="s">
@@ -7098,7 +7105,7 @@
       <c r="B40" t="s">
         <v>488</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="11">
         <v>2023</v>
       </c>
       <c r="D40" t="s">
@@ -7134,7 +7141,7 @@
       <c r="B41" t="s">
         <v>489</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="11">
         <v>2023</v>
       </c>
       <c r="D41" t="s">
@@ -7158,7 +7165,7 @@
       <c r="B42" t="s">
         <v>490</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="11">
         <v>2023</v>
       </c>
       <c r="D42" t="s">
@@ -7194,7 +7201,7 @@
       <c r="B43" t="s">
         <v>491</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="11">
         <v>2023</v>
       </c>
       <c r="D43" t="s">
@@ -7226,7 +7233,7 @@
       <c r="B44" t="s">
         <v>493</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="11">
         <v>2023</v>
       </c>
       <c r="D44" t="s">
@@ -7262,7 +7269,7 @@
       <c r="B45" t="s">
         <v>494</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="11">
         <v>2023</v>
       </c>
       <c r="D45" t="s">
@@ -7296,7 +7303,7 @@
       <c r="B46" t="s">
         <v>495</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="11">
         <v>2023</v>
       </c>
       <c r="D46" t="s">
@@ -7320,7 +7327,7 @@
       <c r="B47" t="s">
         <v>496</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="11">
         <v>2023</v>
       </c>
       <c r="D47" t="s">
@@ -7344,7 +7351,7 @@
       <c r="B48" t="s">
         <v>497</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="11">
         <v>2023</v>
       </c>
       <c r="D48" t="s">
@@ -7380,7 +7387,7 @@
       <c r="B49" t="s">
         <v>490</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="11">
         <v>2023</v>
       </c>
       <c r="D49" t="s">
@@ -7416,7 +7423,7 @@
       <c r="B50" t="s">
         <v>1713</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="11">
         <v>2023</v>
       </c>
       <c r="D50" t="s">
@@ -7452,7 +7459,7 @@
       <c r="B51" t="s">
         <v>498</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="11">
         <v>2023</v>
       </c>
       <c r="D51" t="s">
@@ -7486,7 +7493,7 @@
       <c r="B52" t="s">
         <v>499</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="11">
         <v>2023</v>
       </c>
       <c r="D52" t="s">
@@ -7518,7 +7525,7 @@
       <c r="B53" t="s">
         <v>532</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="11">
         <v>2023</v>
       </c>
       <c r="D53" t="s">
@@ -7548,7 +7555,7 @@
       <c r="B54" t="s">
         <v>848</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="11">
         <v>2023</v>
       </c>
       <c r="D54" t="s">
@@ -7578,7 +7585,7 @@
       <c r="B55" t="s">
         <v>500</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="11">
         <v>2023</v>
       </c>
       <c r="D55" t="s">
@@ -7612,7 +7619,7 @@
       <c r="B56" t="s">
         <v>458</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="11">
         <v>2023</v>
       </c>
       <c r="D56" t="s">
@@ -7644,7 +7651,7 @@
       <c r="B57" t="s">
         <v>459</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="11">
         <v>2023</v>
       </c>
       <c r="D57" t="s">
@@ -7676,7 +7683,7 @@
       <c r="B58" t="s">
         <v>490</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="11">
         <v>2023</v>
       </c>
       <c r="D58" t="s">
@@ -7706,7 +7713,7 @@
       <c r="B59" t="s">
         <v>501</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="11">
         <v>2022</v>
       </c>
       <c r="D59" t="s">
@@ -7738,7 +7745,7 @@
       <c r="B60" t="s">
         <v>502</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="11">
         <v>2022</v>
       </c>
       <c r="D60" t="s">
@@ -7772,7 +7779,7 @@
       <c r="B61" t="s">
         <v>503</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="11">
         <v>2022</v>
       </c>
       <c r="D61" t="s">
@@ -7804,7 +7811,7 @@
       <c r="B62" t="s">
         <v>460</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="11">
         <v>2022</v>
       </c>
       <c r="D62" t="s">
@@ -7836,7 +7843,7 @@
       <c r="B63" t="s">
         <v>735</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="11">
         <v>2022</v>
       </c>
       <c r="D63" t="s">
@@ -7870,7 +7877,7 @@
       <c r="B64" t="s">
         <v>504</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="11">
         <v>2022</v>
       </c>
       <c r="D64" t="s">
@@ -7904,7 +7911,7 @@
       <c r="B65" t="s">
         <v>495</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="11">
         <v>2022</v>
       </c>
       <c r="D65" t="s">
@@ -7938,7 +7945,7 @@
       <c r="B66" t="s">
         <v>505</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="11">
         <v>2022</v>
       </c>
       <c r="D66" t="s">
@@ -7974,7 +7981,7 @@
       <c r="B67" t="s">
         <v>736</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="11">
         <v>2022</v>
       </c>
       <c r="D67" t="s">
@@ -7998,7 +8005,7 @@
       <c r="B68" t="s">
         <v>506</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="11">
         <v>2022</v>
       </c>
       <c r="D68" t="s">
@@ -8022,7 +8029,7 @@
       <c r="B69" t="s">
         <v>508</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="11">
         <v>2022</v>
       </c>
       <c r="D69" t="s">
@@ -8056,7 +8063,7 @@
       <c r="B70" t="s">
         <v>509</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="11">
         <v>2022</v>
       </c>
       <c r="D70" t="s">
@@ -8092,7 +8099,7 @@
       <c r="B71" t="s">
         <v>758</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="11">
         <v>2022</v>
       </c>
       <c r="D71" t="s">
@@ -8122,7 +8129,7 @@
       <c r="B72" t="s">
         <v>1810</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="11">
         <v>2022</v>
       </c>
       <c r="D72" t="s">
@@ -8152,7 +8159,7 @@
       <c r="B73" t="s">
         <v>527</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="11">
         <v>2022</v>
       </c>
       <c r="D73" t="s">
@@ -8188,7 +8195,7 @@
       <c r="B74" t="s">
         <v>507</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="11">
         <v>2021</v>
       </c>
       <c r="D74" t="s">
@@ -8220,7 +8227,7 @@
       <c r="B75" t="s">
         <v>510</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="11">
         <v>2021</v>
       </c>
       <c r="D75" t="s">
@@ -8244,7 +8251,7 @@
       <c r="B76" t="s">
         <v>511</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="11">
         <v>2021</v>
       </c>
       <c r="D76" t="s">
@@ -8276,7 +8283,7 @@
       <c r="B77" t="s">
         <v>458</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="11">
         <v>2021</v>
       </c>
       <c r="D77" t="s">
@@ -8308,7 +8315,7 @@
       <c r="B78" t="s">
         <v>1721</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="11">
         <v>2021</v>
       </c>
       <c r="D78" t="s">
@@ -8340,7 +8347,7 @@
       <c r="B79" t="s">
         <v>499</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="11">
         <v>2021</v>
       </c>
       <c r="D79" t="s">
@@ -8376,7 +8383,7 @@
       <c r="B80" t="s">
         <v>512</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="11">
         <v>2021</v>
       </c>
       <c r="D80" t="s">
@@ -8410,7 +8417,7 @@
       <c r="B81" t="s">
         <v>513</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="11">
         <v>2021</v>
       </c>
       <c r="D81" t="s">
@@ -8446,7 +8453,7 @@
       <c r="B82" t="s">
         <v>514</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="11">
         <v>2021</v>
       </c>
       <c r="D82" t="s">
@@ -8480,7 +8487,7 @@
       <c r="B83" t="s">
         <v>515</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="11">
         <v>2021</v>
       </c>
       <c r="D83" t="s">
@@ -8516,7 +8523,7 @@
       <c r="B84" t="s">
         <v>818</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="11">
         <v>2021</v>
       </c>
       <c r="D84" t="s">
@@ -8552,7 +8559,7 @@
       <c r="B85" t="s">
         <v>820</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="11">
         <v>2021</v>
       </c>
       <c r="D85" t="s">
@@ -8588,7 +8595,7 @@
       <c r="B86" t="s">
         <v>516</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="11">
         <v>2021</v>
       </c>
       <c r="D86" t="s">
@@ -8616,7 +8623,7 @@
       <c r="B87" t="s">
         <v>517</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="11">
         <v>2021</v>
       </c>
       <c r="D87" t="s">
@@ -8652,7 +8659,7 @@
       <c r="B88" t="s">
         <v>461</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="11">
         <v>2021</v>
       </c>
       <c r="D88" t="s">
@@ -8684,7 +8691,7 @@
       <c r="B89" t="s">
         <v>822</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="11">
         <v>2021</v>
       </c>
       <c r="D89" t="s">
@@ -8716,7 +8723,7 @@
       <c r="B90" t="s">
         <v>458</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="11">
         <v>2021</v>
       </c>
       <c r="D90" t="s">
@@ -8748,7 +8755,7 @@
       <c r="B91" t="s">
         <v>462</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="11">
         <v>2021</v>
       </c>
       <c r="D91" t="s">
@@ -8780,7 +8787,7 @@
       <c r="B92" t="s">
         <v>518</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="11">
         <v>2021</v>
       </c>
       <c r="D92" t="s">
@@ -8816,7 +8823,7 @@
       <c r="B93" t="s">
         <v>519</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="11">
         <v>2020</v>
       </c>
       <c r="D93" t="s">
@@ -8850,7 +8857,7 @@
       <c r="B94" t="s">
         <v>520</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="11">
         <v>2020</v>
       </c>
       <c r="D94" t="s">
@@ -8884,7 +8891,7 @@
       <c r="B95" t="s">
         <v>521</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="11">
         <v>2020</v>
       </c>
       <c r="D95" t="s">
@@ -8920,7 +8927,7 @@
       <c r="B96" t="s">
         <v>522</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="11">
         <v>2020</v>
       </c>
       <c r="D96" t="s">
@@ -8956,7 +8963,7 @@
       <c r="B97" t="s">
         <v>524</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="11">
         <v>2020</v>
       </c>
       <c r="D97" t="s">
@@ -8992,7 +8999,7 @@
       <c r="B98" t="s">
         <v>512</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="11">
         <v>2020</v>
       </c>
       <c r="D98" t="s">
@@ -9028,7 +9035,7 @@
       <c r="B99" t="s">
         <v>830</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="11">
         <v>2020</v>
       </c>
       <c r="D99" t="s">
@@ -9060,7 +9067,7 @@
       <c r="B100" t="s">
         <v>525</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="11">
         <v>2020</v>
       </c>
       <c r="D100" t="s">
@@ -9094,7 +9101,7 @@
       <c r="B101" t="s">
         <v>526</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="11">
         <v>2020</v>
       </c>
       <c r="D101" t="s">
@@ -9128,7 +9135,7 @@
       <c r="B102" t="s">
         <v>528</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="11">
         <v>2020</v>
       </c>
       <c r="D102" t="s">
@@ -9162,7 +9169,7 @@
       <c r="B103" t="s">
         <v>529</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="11">
         <v>2020</v>
       </c>
       <c r="D103" t="s">
@@ -9198,7 +9205,7 @@
       <c r="B104" t="s">
         <v>530</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="11">
         <v>2020</v>
       </c>
       <c r="D104" t="s">
@@ -9232,7 +9239,7 @@
       <c r="B105" t="s">
         <v>836</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="11">
         <v>2020</v>
       </c>
       <c r="D105" t="s">
@@ -9268,7 +9275,7 @@
       <c r="B106" t="s">
         <v>531</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="11">
         <v>2020</v>
       </c>
       <c r="D106" t="s">
@@ -9302,7 +9309,7 @@
       <c r="B107" t="s">
         <v>529</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="11">
         <v>2020</v>
       </c>
       <c r="D107" t="s">
@@ -9338,7 +9345,7 @@
       <c r="B108" t="s">
         <v>1714</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="11">
         <v>2020</v>
       </c>
       <c r="D108" t="s">
@@ -9366,7 +9373,7 @@
       <c r="B109" t="s">
         <v>532</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="11">
         <v>2020</v>
       </c>
       <c r="D109" t="s">
@@ -9400,7 +9407,7 @@
       <c r="B110" t="s">
         <v>495</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="11">
         <v>2020</v>
       </c>
       <c r="D110" t="s">
@@ -9434,7 +9441,7 @@
       <c r="B111" t="s">
         <v>1715</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="11">
         <v>2020</v>
       </c>
       <c r="D111" t="s">
@@ -9468,7 +9475,7 @@
       <c r="B112" t="s">
         <v>543</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="11">
         <v>2020</v>
       </c>
       <c r="D112" t="s">
@@ -9504,7 +9511,7 @@
       <c r="B113" t="s">
         <v>529</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="11">
         <v>2020</v>
       </c>
       <c r="D113" t="s">
@@ -9540,7 +9547,7 @@
       <c r="B114" t="s">
         <v>523</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="11">
         <v>2019</v>
       </c>
       <c r="D114" t="s">
@@ -9572,7 +9579,7 @@
       <c r="B115" t="s">
         <v>533</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="11">
         <v>2019</v>
       </c>
       <c r="D115" t="s">
@@ -9600,7 +9607,7 @@
       <c r="B116" t="s">
         <v>534</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="11">
         <v>2019</v>
       </c>
       <c r="D116" t="s">
@@ -9628,7 +9635,7 @@
       <c r="B117" t="s">
         <v>535</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="11">
         <v>2019</v>
       </c>
       <c r="D117" t="s">
@@ -9650,7 +9657,7 @@
       <c r="B118" t="s">
         <v>510</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="11">
         <v>2019</v>
       </c>
       <c r="D118" t="s">
@@ -9682,7 +9689,7 @@
       <c r="B119" t="s">
         <v>100</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="11">
         <v>2019</v>
       </c>
       <c r="D119" t="s">
@@ -9704,7 +9711,7 @@
       <c r="B120" t="s">
         <v>499</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="11">
         <v>2019</v>
       </c>
       <c r="D120" t="s">
@@ -9740,7 +9747,7 @@
       <c r="B121" t="s">
         <v>98</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="11">
         <v>2019</v>
       </c>
       <c r="D121" t="s">
@@ -9776,7 +9783,7 @@
       <c r="B122" t="s">
         <v>100</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="11">
         <v>2019</v>
       </c>
       <c r="D122" t="s">
@@ -9812,7 +9819,7 @@
       <c r="B123" t="s">
         <v>536</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="11">
         <v>2019</v>
       </c>
       <c r="D123" t="s">
@@ -9846,7 +9853,7 @@
       <c r="B124" t="s">
         <v>537</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="11">
         <v>2019</v>
       </c>
       <c r="D124" t="s">
@@ -9882,7 +9889,7 @@
       <c r="B125" t="s">
         <v>463</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="11">
         <v>2019</v>
       </c>
       <c r="D125" t="s">
@@ -9916,7 +9923,7 @@
       <c r="B126" t="s">
         <v>1014</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="11">
         <v>2019</v>
       </c>
       <c r="D126" t="s">
@@ -9948,7 +9955,7 @@
       <c r="B127" t="s">
         <v>464</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="11">
         <v>2019</v>
       </c>
       <c r="D127" t="s">
@@ -9982,7 +9989,7 @@
       <c r="B128" t="s">
         <v>538</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="11">
         <v>2019</v>
       </c>
       <c r="D128" t="s">
@@ -10014,7 +10021,7 @@
       <c r="B129" t="s">
         <v>539</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="11">
         <v>2019</v>
       </c>
       <c r="D129" t="s">
@@ -10050,7 +10057,7 @@
       <c r="B130" t="s">
         <v>540</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="11">
         <v>2019</v>
       </c>
       <c r="D130" t="s">
@@ -10084,7 +10091,7 @@
       <c r="B131" t="s">
         <v>541</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="11">
         <v>2019</v>
       </c>
       <c r="D131" t="s">
@@ -10116,7 +10123,7 @@
       <c r="B132" t="s">
         <v>1030</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="11">
         <v>2019</v>
       </c>
       <c r="D132" t="s">
@@ -10152,7 +10159,7 @@
       <c r="B133" t="s">
         <v>113</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="11">
         <v>2019</v>
       </c>
       <c r="D133" t="s">
@@ -10188,7 +10195,7 @@
       <c r="B134" t="s">
         <v>542</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="11">
         <v>2019</v>
       </c>
       <c r="D134" t="s">
@@ -10224,7 +10231,7 @@
       <c r="B135" t="s">
         <v>113</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="11">
         <v>2019</v>
       </c>
       <c r="D135" t="s">
@@ -10260,7 +10267,7 @@
       <c r="B136" t="s">
         <v>543</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="11">
         <v>2019</v>
       </c>
       <c r="D136" t="s">
@@ -10296,7 +10303,7 @@
       <c r="B137" t="s">
         <v>529</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="11">
         <v>2019</v>
       </c>
       <c r="D137" t="s">
@@ -10332,7 +10339,7 @@
       <c r="B138" t="s">
         <v>544</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="11">
         <v>2019</v>
       </c>
       <c r="D138" t="s">
@@ -10366,7 +10373,7 @@
       <c r="B139" t="s">
         <v>1047</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="11">
         <v>2018</v>
       </c>
       <c r="D139" t="s">
@@ -10398,7 +10405,7 @@
       <c r="B140" t="s">
         <v>545</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="11">
         <v>2018</v>
       </c>
       <c r="D140" t="s">
@@ -10430,7 +10437,7 @@
       <c r="B141" t="s">
         <v>546</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="11">
         <v>2018</v>
       </c>
       <c r="D141" t="s">
@@ -10466,7 +10473,7 @@
       <c r="B142" t="s">
         <v>512</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="11">
         <v>2018</v>
       </c>
       <c r="D142" t="s">
@@ -10496,7 +10503,7 @@
       <c r="B143" t="s">
         <v>463</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="11">
         <v>2018</v>
       </c>
       <c r="D143" t="s">
@@ -10528,7 +10535,7 @@
       <c r="B144" t="s">
         <v>547</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="11">
         <v>2018</v>
       </c>
       <c r="D144" t="s">
@@ -10552,7 +10559,7 @@
       <c r="B145" t="s">
         <v>1716</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="11">
         <v>2018</v>
       </c>
       <c r="D145" t="s">
@@ -10588,7 +10595,7 @@
       <c r="B146" t="s">
         <v>1717</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="11">
         <v>2018</v>
       </c>
       <c r="D146" t="s">
@@ -10622,7 +10629,7 @@
       <c r="B147" t="s">
         <v>542</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="11">
         <v>2018</v>
       </c>
       <c r="D147" t="s">
@@ -10656,7 +10663,7 @@
       <c r="B148" t="s">
         <v>543</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="11">
         <v>2018</v>
       </c>
       <c r="D148" t="s">
@@ -10690,7 +10697,7 @@
       <c r="B149" t="s">
         <v>542</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="11">
         <v>2018</v>
       </c>
       <c r="D149" t="s">
@@ -10724,7 +10731,7 @@
       <c r="B150" t="s">
         <v>543</v>
       </c>
-      <c r="C150">
+      <c r="C150" s="11">
         <v>2018</v>
       </c>
       <c r="D150" t="s">
@@ -10760,7 +10767,7 @@
       <c r="B151" t="s">
         <v>548</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="11">
         <v>2018</v>
       </c>
       <c r="D151" t="s">
@@ -10796,7 +10803,7 @@
       <c r="B152" t="s">
         <v>1079</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="11">
         <v>2018</v>
       </c>
       <c r="D152" t="s">
@@ -10832,7 +10839,7 @@
       <c r="B153" t="s">
         <v>551</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="11">
         <v>2018</v>
       </c>
       <c r="D153" t="s">
@@ -10868,7 +10875,7 @@
       <c r="B154" t="s">
         <v>1719</v>
       </c>
-      <c r="C154">
+      <c r="C154" s="11">
         <v>2018</v>
       </c>
       <c r="D154" t="s">
@@ -10890,7 +10897,7 @@
       <c r="B155" t="s">
         <v>1719</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="11">
         <v>2018</v>
       </c>
       <c r="D155" t="s">
@@ -10912,7 +10919,7 @@
       <c r="B156" t="s">
         <v>550</v>
       </c>
-      <c r="C156">
+      <c r="C156" s="11">
         <v>2017</v>
       </c>
       <c r="D156" t="s">
@@ -10948,7 +10955,7 @@
       <c r="B157" t="s">
         <v>549</v>
       </c>
-      <c r="C157">
+      <c r="C157" s="11">
         <v>2017</v>
       </c>
       <c r="D157" t="s">
@@ -10984,7 +10991,7 @@
       <c r="B158" t="s">
         <v>113</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="11">
         <v>2017</v>
       </c>
       <c r="D158" t="s">
@@ -11018,7 +11025,7 @@
       <c r="B159" t="s">
         <v>1083</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="11">
         <v>2017</v>
       </c>
       <c r="D159" t="s">
@@ -11050,7 +11057,7 @@
       <c r="B160" t="s">
         <v>552</v>
       </c>
-      <c r="C160">
+      <c r="C160" s="11">
         <v>2017</v>
       </c>
       <c r="D160" t="s">
@@ -11084,7 +11091,7 @@
       <c r="B161" t="s">
         <v>1718</v>
       </c>
-      <c r="C161">
+      <c r="C161" s="11">
         <v>2017</v>
       </c>
       <c r="D161" t="s">
@@ -11118,7 +11125,7 @@
       <c r="B162" t="s">
         <v>725</v>
       </c>
-      <c r="C162">
+      <c r="C162" s="11">
         <v>2017</v>
       </c>
       <c r="D162" t="s">
@@ -11154,7 +11161,7 @@
       <c r="B163" t="s">
         <v>138</v>
       </c>
-      <c r="C163">
+      <c r="C163" s="11">
         <v>2017</v>
       </c>
       <c r="D163" t="s">
@@ -11188,7 +11195,7 @@
       <c r="B164" t="s">
         <v>553</v>
       </c>
-      <c r="C164">
+      <c r="C164" s="11">
         <v>2017</v>
       </c>
       <c r="D164" t="s">
@@ -11224,7 +11231,7 @@
       <c r="B165" t="s">
         <v>1720</v>
       </c>
-      <c r="C165">
+      <c r="C165" s="11">
         <v>2017</v>
       </c>
       <c r="D165" t="s">
@@ -11260,7 +11267,7 @@
       <c r="B166" t="s">
         <v>554</v>
       </c>
-      <c r="C166">
+      <c r="C166" s="11">
         <v>2017</v>
       </c>
       <c r="D166" t="s">
@@ -11290,7 +11297,7 @@
       <c r="B167" t="s">
         <v>495</v>
       </c>
-      <c r="C167">
+      <c r="C167" s="11">
         <v>2017</v>
       </c>
       <c r="D167" t="s">
@@ -11314,7 +11321,7 @@
       <c r="B168" t="s">
         <v>542</v>
       </c>
-      <c r="C168">
+      <c r="C168" s="11">
         <v>2017</v>
       </c>
       <c r="D168" t="s">
@@ -11350,7 +11357,7 @@
       <c r="B169" t="s">
         <v>555</v>
       </c>
-      <c r="C169">
+      <c r="C169" s="11">
         <v>2016</v>
       </c>
       <c r="D169" t="s">
@@ -11382,7 +11389,7 @@
       <c r="B170" t="s">
         <v>1108</v>
       </c>
-      <c r="C170">
+      <c r="C170" s="11">
         <v>2016</v>
       </c>
       <c r="D170" t="s">
@@ -11414,7 +11421,7 @@
       <c r="B171" t="s">
         <v>556</v>
       </c>
-      <c r="C171">
+      <c r="C171" s="11">
         <v>2016</v>
       </c>
       <c r="D171" t="s">
@@ -11448,7 +11455,7 @@
       <c r="B172" t="s">
         <v>495</v>
       </c>
-      <c r="C172">
+      <c r="C172" s="11">
         <v>2016</v>
       </c>
       <c r="D172" t="s">
@@ -11472,7 +11479,7 @@
       <c r="B173" t="s">
         <v>557</v>
       </c>
-      <c r="C173">
+      <c r="C173" s="11">
         <v>2016</v>
       </c>
       <c r="D173" t="s">
@@ -11504,7 +11511,7 @@
       <c r="B174" t="s">
         <v>558</v>
       </c>
-      <c r="C174">
+      <c r="C174" s="11">
         <v>2016</v>
       </c>
       <c r="D174" t="s">
@@ -11536,7 +11543,7 @@
       <c r="B175" t="s">
         <v>559</v>
       </c>
-      <c r="C175">
+      <c r="C175" s="11">
         <v>2016</v>
       </c>
       <c r="D175" t="s">
@@ -11568,7 +11575,7 @@
       <c r="B176" t="s">
         <v>1706</v>
       </c>
-      <c r="C176">
+      <c r="C176" s="11">
         <v>2016</v>
       </c>
       <c r="D176" t="s">
@@ -11600,7 +11607,7 @@
       <c r="B177" t="s">
         <v>465</v>
       </c>
-      <c r="C177">
+      <c r="C177" s="11">
         <v>2016</v>
       </c>
       <c r="D177" t="s">
@@ -11632,7 +11639,7 @@
       <c r="B178" t="s">
         <v>1712</v>
       </c>
-      <c r="C178">
+      <c r="C178" s="11">
         <v>2016</v>
       </c>
       <c r="D178" t="s">
@@ -11664,7 +11671,7 @@
       <c r="B179" t="s">
         <v>466</v>
       </c>
-      <c r="C179">
+      <c r="C179" s="11">
         <v>2016</v>
       </c>
       <c r="D179" t="s">
@@ -11696,7 +11703,7 @@
       <c r="B180" t="s">
         <v>542</v>
       </c>
-      <c r="C180">
+      <c r="C180" s="11">
         <v>2016</v>
       </c>
       <c r="D180" t="s">
@@ -11728,7 +11735,7 @@
       <c r="B181" t="s">
         <v>1131</v>
       </c>
-      <c r="C181">
+      <c r="C181" s="11">
         <v>2016</v>
       </c>
       <c r="D181" t="s">
@@ -11760,7 +11767,7 @@
       <c r="B182" t="s">
         <v>1135</v>
       </c>
-      <c r="C182">
+      <c r="C182" s="11">
         <v>2016</v>
       </c>
       <c r="D182" t="s">
@@ -11792,7 +11799,7 @@
       <c r="B183" t="s">
         <v>560</v>
       </c>
-      <c r="C183">
+      <c r="C183" s="11">
         <v>2016</v>
       </c>
       <c r="D183" t="s">
@@ -11826,7 +11833,7 @@
       <c r="B184" t="s">
         <v>561</v>
       </c>
-      <c r="C184">
+      <c r="C184" s="11">
         <v>2016</v>
       </c>
       <c r="D184" t="s">
@@ -11850,7 +11857,7 @@
       <c r="B185" t="s">
         <v>1141</v>
       </c>
-      <c r="C185">
+      <c r="C185" s="11">
         <v>2016</v>
       </c>
       <c r="D185" t="s">
@@ -11886,7 +11893,7 @@
       <c r="B186" t="s">
         <v>495</v>
       </c>
-      <c r="C186">
+      <c r="C186" s="11">
         <v>2016</v>
       </c>
       <c r="D186" t="s">
@@ -11920,7 +11927,7 @@
       <c r="B187" t="s">
         <v>562</v>
       </c>
-      <c r="C187">
+      <c r="C187" s="11">
         <v>2016</v>
       </c>
       <c r="D187" t="s">
@@ -11956,7 +11963,7 @@
       <c r="B188" t="s">
         <v>495</v>
       </c>
-      <c r="C188">
+      <c r="C188" s="11">
         <v>2016</v>
       </c>
       <c r="D188" t="s">
@@ -11990,7 +11997,7 @@
       <c r="B189" t="s">
         <v>563</v>
       </c>
-      <c r="C189">
+      <c r="C189" s="11">
         <v>2016</v>
       </c>
       <c r="D189" t="s">
@@ -12026,7 +12033,7 @@
       <c r="B190" t="s">
         <v>1155</v>
       </c>
-      <c r="C190">
+      <c r="C190" s="11">
         <v>2016</v>
       </c>
       <c r="D190" t="s">
@@ -12062,7 +12069,7 @@
       <c r="B191" t="s">
         <v>564</v>
       </c>
-      <c r="C191">
+      <c r="C191" s="11">
         <v>2016</v>
       </c>
       <c r="D191" t="s">
@@ -12098,7 +12105,7 @@
       <c r="B192" t="s">
         <v>1707</v>
       </c>
-      <c r="C192">
+      <c r="C192" s="11">
         <v>2016</v>
       </c>
       <c r="D192" t="s">
@@ -12134,7 +12141,7 @@
       <c r="B193" t="s">
         <v>565</v>
       </c>
-      <c r="C193">
+      <c r="C193" s="11">
         <v>2015</v>
       </c>
       <c r="D193" t="s">
@@ -12166,7 +12173,7 @@
       <c r="B194" t="s">
         <v>566</v>
       </c>
-      <c r="C194">
+      <c r="C194" s="11">
         <v>2015</v>
       </c>
       <c r="D194" t="s">
@@ -12190,7 +12197,7 @@
       <c r="B195" t="s">
         <v>167</v>
       </c>
-      <c r="C195">
+      <c r="C195" s="11">
         <v>2015</v>
       </c>
       <c r="D195" t="s">
@@ -12214,7 +12221,7 @@
       <c r="B196" t="s">
         <v>169</v>
       </c>
-      <c r="C196">
+      <c r="C196" s="11">
         <v>2015</v>
       </c>
       <c r="D196" t="s">
@@ -12246,7 +12253,7 @@
       <c r="B197" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="C197" s="6">
+      <c r="C197" s="12">
         <v>2015</v>
       </c>
       <c r="D197" s="3" t="s">
@@ -12270,7 +12277,7 @@
       <c r="B198" t="s">
         <v>467</v>
       </c>
-      <c r="C198">
+      <c r="C198" s="11">
         <v>2015</v>
       </c>
       <c r="D198" t="s">
@@ -12306,7 +12313,7 @@
       <c r="B199" t="s">
         <v>468</v>
       </c>
-      <c r="C199">
+      <c r="C199" s="11">
         <v>2015</v>
       </c>
       <c r="D199" t="s">
@@ -12338,7 +12345,7 @@
       <c r="B200" t="s">
         <v>469</v>
       </c>
-      <c r="C200">
+      <c r="C200" s="11">
         <v>2015</v>
       </c>
       <c r="D200" t="s">
@@ -12370,7 +12377,7 @@
       <c r="B201" t="s">
         <v>603</v>
       </c>
-      <c r="C201">
+      <c r="C201" s="11">
         <v>2015</v>
       </c>
       <c r="D201" t="s">
@@ -12404,7 +12411,7 @@
       <c r="B202" t="s">
         <v>568</v>
       </c>
-      <c r="C202">
+      <c r="C202" s="11">
         <v>2015</v>
       </c>
       <c r="D202" t="s">
@@ -12438,7 +12445,7 @@
       <c r="B203" t="s">
         <v>569</v>
       </c>
-      <c r="C203">
+      <c r="C203" s="11">
         <v>2015</v>
       </c>
       <c r="D203" t="s">
@@ -12472,7 +12479,7 @@
       <c r="B204" t="s">
         <v>570</v>
       </c>
-      <c r="C204">
+      <c r="C204" s="11">
         <v>2015</v>
       </c>
       <c r="D204" t="s">
@@ -12508,7 +12515,7 @@
       <c r="B205" t="s">
         <v>571</v>
       </c>
-      <c r="C205">
+      <c r="C205" s="11">
         <v>2015</v>
       </c>
       <c r="D205" t="s">
@@ -12532,7 +12539,7 @@
       <c r="B206" t="s">
         <v>572</v>
       </c>
-      <c r="C206">
+      <c r="C206" s="11">
         <v>2015</v>
       </c>
       <c r="D206" t="s">
@@ -12566,7 +12573,7 @@
       <c r="B207" t="s">
         <v>723</v>
       </c>
-      <c r="C207">
+      <c r="C207" s="11">
         <v>2015</v>
       </c>
       <c r="D207" t="s">
@@ -12600,7 +12607,7 @@
       <c r="B208" t="s">
         <v>573</v>
       </c>
-      <c r="C208">
+      <c r="C208" s="11">
         <v>2015</v>
       </c>
       <c r="D208" t="s">
@@ -12636,7 +12643,7 @@
       <c r="B209" t="s">
         <v>1705</v>
       </c>
-      <c r="C209">
+      <c r="C209" s="11">
         <v>2015</v>
       </c>
       <c r="D209" t="s">
@@ -12672,7 +12679,7 @@
       <c r="B210" t="s">
         <v>589</v>
       </c>
-      <c r="C210">
+      <c r="C210" s="11">
         <v>2015</v>
       </c>
       <c r="D210" t="s">
@@ -12708,7 +12715,7 @@
       <c r="B211" t="s">
         <v>1723</v>
       </c>
-      <c r="C211">
+      <c r="C211" s="11">
         <v>2015</v>
       </c>
       <c r="D211" t="s">
@@ -12740,7 +12747,7 @@
       <c r="B212" t="s">
         <v>551</v>
       </c>
-      <c r="C212">
+      <c r="C212" s="11">
         <v>2015</v>
       </c>
       <c r="D212" t="s">
@@ -12772,7 +12779,7 @@
       <c r="B213" t="s">
         <v>1704</v>
       </c>
-      <c r="C213">
+      <c r="C213" s="11">
         <v>2015</v>
       </c>
       <c r="D213" t="s">
@@ -12806,7 +12813,7 @@
       <c r="B214" t="s">
         <v>595</v>
       </c>
-      <c r="C214">
+      <c r="C214" s="11">
         <v>2015</v>
       </c>
       <c r="D214" t="s">
@@ -12838,7 +12845,7 @@
       <c r="B215" t="s">
         <v>737</v>
       </c>
-      <c r="C215">
+      <c r="C215" s="11">
         <v>2015</v>
       </c>
       <c r="D215" t="s">
@@ -12870,7 +12877,7 @@
       <c r="B216" t="s">
         <v>575</v>
       </c>
-      <c r="C216">
+      <c r="C216" s="11">
         <v>2015</v>
       </c>
       <c r="D216" t="s">
@@ -12902,7 +12909,7 @@
       <c r="B217" t="s">
         <v>576</v>
       </c>
-      <c r="C217">
+      <c r="C217" s="11">
         <v>2015</v>
       </c>
       <c r="D217" t="s">
@@ -12938,7 +12945,7 @@
       <c r="B218" t="s">
         <v>465</v>
       </c>
-      <c r="C218">
+      <c r="C218" s="11">
         <v>2015</v>
       </c>
       <c r="D218" t="s">
@@ -12972,7 +12979,7 @@
       <c r="B219" t="s">
         <v>577</v>
       </c>
-      <c r="C219">
+      <c r="C219" s="11">
         <v>2015</v>
       </c>
       <c r="D219" t="s">
@@ -13004,7 +13011,7 @@
       <c r="B220" t="s">
         <v>742</v>
       </c>
-      <c r="C220">
+      <c r="C220" s="11">
         <v>2015</v>
       </c>
       <c r="D220" t="s">
@@ -13036,7 +13043,7 @@
       <c r="B221" t="s">
         <v>743</v>
       </c>
-      <c r="C221">
+      <c r="C221" s="11">
         <v>2015</v>
       </c>
       <c r="D221" t="s">
@@ -13060,7 +13067,7 @@
       <c r="B222" t="s">
         <v>574</v>
       </c>
-      <c r="C222">
+      <c r="C222" s="11">
         <v>2014</v>
       </c>
       <c r="D222" t="s">
@@ -13096,7 +13103,7 @@
       <c r="B223" t="s">
         <v>560</v>
       </c>
-      <c r="C223">
+      <c r="C223" s="11">
         <v>2014</v>
       </c>
       <c r="D223" t="s">
@@ -13128,7 +13135,7 @@
       <c r="B224" t="s">
         <v>741</v>
       </c>
-      <c r="C224">
+      <c r="C224" s="11">
         <v>2014</v>
       </c>
       <c r="D224" t="s">
@@ -13160,7 +13167,7 @@
       <c r="B225" t="s">
         <v>578</v>
       </c>
-      <c r="C225">
+      <c r="C225" s="11">
         <v>2014</v>
       </c>
       <c r="D225" t="s">
@@ -13192,7 +13199,7 @@
       <c r="B226" t="s">
         <v>1726</v>
       </c>
-      <c r="C226">
+      <c r="C226" s="11">
         <v>2014</v>
       </c>
       <c r="D226" t="s">
@@ -13224,7 +13231,7 @@
       <c r="B227" t="s">
         <v>579</v>
       </c>
-      <c r="C227">
+      <c r="C227" s="11">
         <v>2014</v>
       </c>
       <c r="D227" t="s">
@@ -13256,7 +13263,7 @@
       <c r="B228" t="s">
         <v>580</v>
       </c>
-      <c r="C228">
+      <c r="C228" s="11">
         <v>2014</v>
       </c>
       <c r="D228" t="s">
@@ -13288,7 +13295,7 @@
       <c r="B229" t="s">
         <v>581</v>
       </c>
-      <c r="C229">
+      <c r="C229" s="11">
         <v>2014</v>
       </c>
       <c r="D229" t="s">
@@ -13316,7 +13323,7 @@
       <c r="B230" t="s">
         <v>582</v>
       </c>
-      <c r="C230">
+      <c r="C230" s="11">
         <v>2014</v>
       </c>
       <c r="D230" t="s">
@@ -13348,7 +13355,7 @@
       <c r="B231" t="s">
         <v>583</v>
       </c>
-      <c r="C231">
+      <c r="C231" s="11">
         <v>2014</v>
       </c>
       <c r="D231" t="s">
@@ -13380,7 +13387,7 @@
       <c r="B232" t="s">
         <v>584</v>
       </c>
-      <c r="C232">
+      <c r="C232" s="11">
         <v>2014</v>
       </c>
       <c r="D232" t="s">
@@ -13404,7 +13411,7 @@
       <c r="B233" t="s">
         <v>1274</v>
       </c>
-      <c r="C233">
+      <c r="C233" s="11">
         <v>2014</v>
       </c>
       <c r="D233" t="s">
@@ -13436,7 +13443,7 @@
       <c r="B234" t="s">
         <v>470</v>
       </c>
-      <c r="C234">
+      <c r="C234" s="11">
         <v>2014</v>
       </c>
       <c r="D234" t="s">
@@ -13468,7 +13475,7 @@
       <c r="B235" t="s">
         <v>471</v>
       </c>
-      <c r="C235">
+      <c r="C235" s="11">
         <v>2014</v>
       </c>
       <c r="D235" t="s">
@@ -13492,7 +13499,7 @@
       <c r="B236" t="s">
         <v>472</v>
       </c>
-      <c r="C236">
+      <c r="C236" s="11">
         <v>2014</v>
       </c>
       <c r="D236" t="s">
@@ -13524,7 +13531,7 @@
       <c r="B237" t="s">
         <v>578</v>
       </c>
-      <c r="C237">
+      <c r="C237" s="11">
         <v>2014</v>
       </c>
       <c r="D237" t="s">
@@ -13560,7 +13567,7 @@
       <c r="B238" t="s">
         <v>585</v>
       </c>
-      <c r="C238">
+      <c r="C238" s="11">
         <v>2014</v>
       </c>
       <c r="D238" t="s">
@@ -13596,7 +13603,7 @@
       <c r="B239" t="s">
         <v>587</v>
       </c>
-      <c r="C239">
+      <c r="C239" s="11">
         <v>2014</v>
       </c>
       <c r="D239" t="s">
@@ -13632,7 +13639,7 @@
       <c r="B240" t="s">
         <v>588</v>
       </c>
-      <c r="C240">
+      <c r="C240" s="11">
         <v>2014</v>
       </c>
       <c r="D240" t="s">
@@ -13666,7 +13673,7 @@
       <c r="B241" t="s">
         <v>1708</v>
       </c>
-      <c r="C241">
+      <c r="C241" s="11">
         <v>2014</v>
       </c>
       <c r="D241" t="s">
@@ -13702,7 +13709,7 @@
       <c r="B242" t="s">
         <v>474</v>
       </c>
-      <c r="C242">
+      <c r="C242" s="11">
         <v>2014</v>
       </c>
       <c r="D242" t="s">
@@ -13738,7 +13745,7 @@
       <c r="B243" t="s">
         <v>607</v>
       </c>
-      <c r="C243">
+      <c r="C243" s="11">
         <v>2014</v>
       </c>
       <c r="D243" t="s">
@@ -13772,7 +13779,7 @@
       <c r="B244" t="s">
         <v>726</v>
       </c>
-      <c r="C244">
+      <c r="C244" s="11">
         <v>2014</v>
       </c>
       <c r="D244" t="s">
@@ -13808,7 +13815,7 @@
       <c r="B245" t="s">
         <v>727</v>
       </c>
-      <c r="C245">
+      <c r="C245" s="11">
         <v>2014</v>
       </c>
       <c r="D245" t="s">
@@ -13844,7 +13851,7 @@
       <c r="B246" t="s">
         <v>587</v>
       </c>
-      <c r="C246">
+      <c r="C246" s="11">
         <v>2014</v>
       </c>
       <c r="D246" t="s">
@@ -13880,7 +13887,7 @@
       <c r="B247" t="s">
         <v>590</v>
       </c>
-      <c r="C247">
+      <c r="C247" s="11">
         <v>2014</v>
       </c>
       <c r="D247" t="s">
@@ -13914,7 +13921,7 @@
       <c r="B248" t="s">
         <v>473</v>
       </c>
-      <c r="C248">
+      <c r="C248" s="11">
         <v>2013</v>
       </c>
       <c r="D248" t="s">
@@ -13950,7 +13957,7 @@
       <c r="B249" t="s">
         <v>586</v>
       </c>
-      <c r="C249">
+      <c r="C249" s="11">
         <v>2013</v>
       </c>
       <c r="D249" t="s">
@@ -13986,7 +13993,7 @@
       <c r="B250" t="s">
         <v>467</v>
       </c>
-      <c r="C250">
+      <c r="C250" s="11">
         <v>2013</v>
       </c>
       <c r="D250" t="s">
@@ -14018,7 +14025,7 @@
       <c r="B251" t="s">
         <v>215</v>
       </c>
-      <c r="C251">
+      <c r="C251" s="11">
         <v>2013</v>
       </c>
       <c r="D251" t="s">
@@ -14050,7 +14057,7 @@
       <c r="B252" t="s">
         <v>591</v>
       </c>
-      <c r="C252">
+      <c r="C252" s="11">
         <v>2013</v>
       </c>
       <c r="D252" t="s">
@@ -14078,7 +14085,7 @@
       <c r="B253" t="s">
         <v>592</v>
       </c>
-      <c r="C253">
+      <c r="C253" s="11">
         <v>2013</v>
       </c>
       <c r="D253" t="s">
@@ -14102,7 +14109,7 @@
       <c r="B254" t="s">
         <v>599</v>
       </c>
-      <c r="C254">
+      <c r="C254" s="11">
         <v>2013</v>
       </c>
       <c r="D254" t="s">
@@ -14130,7 +14137,7 @@
       <c r="B255" t="s">
         <v>593</v>
       </c>
-      <c r="C255">
+      <c r="C255" s="11">
         <v>2013</v>
       </c>
       <c r="D255" t="s">
@@ -14154,7 +14161,7 @@
       <c r="B256" t="s">
         <v>594</v>
       </c>
-      <c r="C256">
+      <c r="C256" s="11">
         <v>2013</v>
       </c>
       <c r="D256" t="s">
@@ -14178,7 +14185,7 @@
       <c r="B257" t="s">
         <v>595</v>
       </c>
-      <c r="C257">
+      <c r="C257" s="11">
         <v>2013</v>
       </c>
       <c r="D257" t="s">
@@ -14210,7 +14217,7 @@
       <c r="B258" t="s">
         <v>596</v>
       </c>
-      <c r="C258">
+      <c r="C258" s="11">
         <v>2013</v>
       </c>
       <c r="D258" t="s">
@@ -14242,7 +14249,7 @@
       <c r="B259" t="s">
         <v>215</v>
       </c>
-      <c r="C259">
+      <c r="C259" s="11">
         <v>2013</v>
       </c>
       <c r="D259" t="s">
@@ -14278,7 +14285,7 @@
       <c r="B260" t="s">
         <v>597</v>
       </c>
-      <c r="C260">
+      <c r="C260" s="11">
         <v>2013</v>
       </c>
       <c r="D260" t="s">
@@ -14312,7 +14319,7 @@
       <c r="B261" t="s">
         <v>598</v>
       </c>
-      <c r="C261">
+      <c r="C261" s="11">
         <v>2013</v>
       </c>
       <c r="D261" t="s">
@@ -14346,7 +14353,7 @@
       <c r="B262" t="s">
         <v>599</v>
       </c>
-      <c r="C262">
+      <c r="C262" s="11">
         <v>2013</v>
       </c>
       <c r="D262" t="s">
@@ -14378,7 +14385,7 @@
       <c r="B263" t="s">
         <v>600</v>
       </c>
-      <c r="C263">
+      <c r="C263" s="11">
         <v>2013</v>
       </c>
       <c r="D263" t="s">
@@ -14412,7 +14419,7 @@
       <c r="B264" t="s">
         <v>601</v>
       </c>
-      <c r="C264">
+      <c r="C264" s="11">
         <v>2013</v>
       </c>
       <c r="D264" t="s">
@@ -14446,7 +14453,7 @@
       <c r="B265" t="s">
         <v>602</v>
       </c>
-      <c r="C265">
+      <c r="C265" s="11">
         <v>2013</v>
       </c>
       <c r="D265" t="s">
@@ -14482,7 +14489,7 @@
       <c r="B266" t="s">
         <v>730</v>
       </c>
-      <c r="C266">
+      <c r="C266" s="11">
         <v>2013</v>
       </c>
       <c r="D266" t="s">
@@ -14518,7 +14525,7 @@
       <c r="B267" t="s">
         <v>572</v>
       </c>
-      <c r="C267">
+      <c r="C267" s="11">
         <v>2013</v>
       </c>
       <c r="D267" t="s">
@@ -14552,7 +14559,7 @@
       <c r="B268" t="s">
         <v>574</v>
       </c>
-      <c r="C268">
+      <c r="C268" s="11">
         <v>2013</v>
       </c>
       <c r="D268" t="s">
@@ -14586,7 +14593,7 @@
       <c r="B269" t="s">
         <v>603</v>
       </c>
-      <c r="C269">
+      <c r="C269" s="11">
         <v>2013</v>
       </c>
       <c r="D269" t="s">
@@ -14622,7 +14629,7 @@
       <c r="B270" t="s">
         <v>728</v>
       </c>
-      <c r="C270">
+      <c r="C270" s="11">
         <v>2013</v>
       </c>
       <c r="D270" t="s">
@@ -14658,7 +14665,7 @@
       <c r="B271" t="s">
         <v>588</v>
       </c>
-      <c r="C271">
+      <c r="C271" s="11">
         <v>2013</v>
       </c>
       <c r="D271" t="s">
@@ -14692,7 +14699,7 @@
       <c r="B272" t="s">
         <v>1356</v>
       </c>
-      <c r="C272">
+      <c r="C272" s="11">
         <v>2012</v>
       </c>
       <c r="D272" t="s">
@@ -14720,7 +14727,7 @@
       <c r="B273" t="s">
         <v>475</v>
       </c>
-      <c r="C273">
+      <c r="C273" s="11">
         <v>2012</v>
       </c>
       <c r="D273" t="s">
@@ -14744,7 +14751,7 @@
       <c r="B274" t="s">
         <v>1359</v>
       </c>
-      <c r="C274">
+      <c r="C274" s="11">
         <v>2012</v>
       </c>
       <c r="D274" t="s">
@@ -14772,7 +14779,7 @@
       <c r="B275" t="s">
         <v>604</v>
       </c>
-      <c r="C275">
+      <c r="C275" s="11">
         <v>2012</v>
       </c>
       <c r="D275" t="s">
@@ -14796,7 +14803,7 @@
       <c r="B276" t="s">
         <v>474</v>
       </c>
-      <c r="C276">
+      <c r="C276" s="11">
         <v>2012</v>
       </c>
       <c r="D276" t="s">
@@ -14828,7 +14835,7 @@
       <c r="B277" t="s">
         <v>605</v>
       </c>
-      <c r="C277">
+      <c r="C277" s="11">
         <v>2012</v>
       </c>
       <c r="D277" t="s">
@@ -14850,7 +14857,7 @@
       <c r="B278" t="s">
         <v>605</v>
       </c>
-      <c r="C278">
+      <c r="C278" s="11">
         <v>2012</v>
       </c>
       <c r="D278" t="s">
@@ -14872,7 +14879,7 @@
       <c r="B279" t="s">
         <v>605</v>
       </c>
-      <c r="C279">
+      <c r="C279" s="11">
         <v>2012</v>
       </c>
       <c r="D279" t="s">
@@ -14896,7 +14903,7 @@
       <c r="B280" t="s">
         <v>606</v>
       </c>
-      <c r="C280">
+      <c r="C280" s="11">
         <v>2012</v>
       </c>
       <c r="D280" t="s">
@@ -14928,7 +14935,7 @@
       <c r="B281" t="s">
         <v>606</v>
       </c>
-      <c r="C281">
+      <c r="C281" s="11">
         <v>2012</v>
       </c>
       <c r="D281" t="s">
@@ -14952,7 +14959,7 @@
       <c r="B282" t="s">
         <v>597</v>
       </c>
-      <c r="C282">
+      <c r="C282" s="11">
         <v>2012</v>
       </c>
       <c r="D282" t="s">
@@ -14980,7 +14987,7 @@
       <c r="B283" t="s">
         <v>607</v>
       </c>
-      <c r="C283">
+      <c r="C283" s="11">
         <v>2012</v>
       </c>
       <c r="D283" t="s">
@@ -15008,7 +15015,7 @@
       <c r="B284" t="s">
         <v>608</v>
       </c>
-      <c r="C284">
+      <c r="C284" s="11">
         <v>2012</v>
       </c>
       <c r="D284" t="s">
@@ -15036,7 +15043,7 @@
       <c r="B285" t="s">
         <v>1375</v>
       </c>
-      <c r="C285">
+      <c r="C285" s="11">
         <v>2012</v>
       </c>
       <c r="D285" t="s">
@@ -15064,7 +15071,7 @@
       <c r="B286" t="s">
         <v>609</v>
       </c>
-      <c r="C286">
+      <c r="C286" s="11">
         <v>2012</v>
       </c>
       <c r="D286" t="s">
@@ -15088,7 +15095,7 @@
       <c r="B287" t="s">
         <v>476</v>
       </c>
-      <c r="C287">
+      <c r="C287" s="11">
         <v>2012</v>
       </c>
       <c r="D287" t="s">
@@ -15112,7 +15119,7 @@
       <c r="B288" t="s">
         <v>588</v>
       </c>
-      <c r="C288">
+      <c r="C288" s="11">
         <v>2012</v>
       </c>
       <c r="D288" t="s">
@@ -15146,7 +15153,7 @@
       <c r="B289" t="s">
         <v>597</v>
       </c>
-      <c r="C289">
+      <c r="C289" s="11">
         <v>2012</v>
       </c>
       <c r="D289" t="s">
@@ -15182,7 +15189,7 @@
       <c r="B290" t="s">
         <v>610</v>
       </c>
-      <c r="C290">
+      <c r="C290" s="11">
         <v>2012</v>
       </c>
       <c r="D290" t="s">
@@ -15216,7 +15223,7 @@
       <c r="B291" t="s">
         <v>611</v>
       </c>
-      <c r="C291">
+      <c r="C291" s="11">
         <v>2012</v>
       </c>
       <c r="D291" t="s">
@@ -15250,7 +15257,7 @@
       <c r="B292" t="s">
         <v>495</v>
       </c>
-      <c r="C292">
+      <c r="C292" s="11">
         <v>2012</v>
       </c>
       <c r="D292" t="s">
@@ -15286,7 +15293,7 @@
       <c r="B293" t="s">
         <v>495</v>
       </c>
-      <c r="C293">
+      <c r="C293" s="11">
         <v>2012</v>
       </c>
       <c r="D293" t="s">
@@ -15322,7 +15329,7 @@
       <c r="B294" t="s">
         <v>1391</v>
       </c>
-      <c r="C294">
+      <c r="C294" s="11">
         <v>2012</v>
       </c>
       <c r="D294" t="s">
@@ -15356,7 +15363,7 @@
       <c r="B295" t="s">
         <v>612</v>
       </c>
-      <c r="C295">
+      <c r="C295" s="11">
         <v>2012</v>
       </c>
       <c r="D295" t="s">
@@ -15380,7 +15387,7 @@
       <c r="B296" t="s">
         <v>613</v>
       </c>
-      <c r="C296">
+      <c r="C296" s="11">
         <v>2012</v>
       </c>
       <c r="D296" t="s">
@@ -15404,7 +15411,7 @@
       <c r="B297" t="s">
         <v>625</v>
       </c>
-      <c r="C297">
+      <c r="C297" s="11">
         <v>2011</v>
       </c>
       <c r="D297" t="s">
@@ -15432,7 +15439,7 @@
       <c r="B298" t="s">
         <v>614</v>
       </c>
-      <c r="C298">
+      <c r="C298" s="11">
         <v>2011</v>
       </c>
       <c r="D298" t="s">
@@ -15454,7 +15461,7 @@
       <c r="B299" t="s">
         <v>615</v>
       </c>
-      <c r="C299">
+      <c r="C299" s="11">
         <v>2011</v>
       </c>
       <c r="D299" t="s">
@@ -15490,7 +15497,7 @@
       <c r="B300" t="s">
         <v>718</v>
       </c>
-      <c r="C300">
+      <c r="C300" s="11">
         <v>2011</v>
       </c>
       <c r="D300" t="s">
@@ -15526,7 +15533,7 @@
       <c r="B301" t="s">
         <v>495</v>
       </c>
-      <c r="C301">
+      <c r="C301" s="11">
         <v>2011</v>
       </c>
       <c r="D301" t="s">
@@ -15562,7 +15569,7 @@
       <c r="B302" t="s">
         <v>616</v>
       </c>
-      <c r="C302">
+      <c r="C302" s="11">
         <v>2011</v>
       </c>
       <c r="D302" t="s">
@@ -15598,7 +15605,7 @@
       <c r="B303" t="s">
         <v>617</v>
       </c>
-      <c r="C303">
+      <c r="C303" s="11">
         <v>2011</v>
       </c>
       <c r="D303" t="s">
@@ -15634,7 +15641,7 @@
       <c r="B304" t="s">
         <v>1409</v>
       </c>
-      <c r="C304">
+      <c r="C304" s="11">
         <v>2011</v>
       </c>
       <c r="D304" t="s">
@@ -15668,7 +15675,7 @@
       <c r="B305" t="s">
         <v>618</v>
       </c>
-      <c r="C305">
+      <c r="C305" s="11">
         <v>2011</v>
       </c>
       <c r="D305" t="s">
@@ -15704,7 +15711,7 @@
       <c r="B306" t="s">
         <v>619</v>
       </c>
-      <c r="C306">
+      <c r="C306" s="11">
         <v>2011</v>
       </c>
       <c r="D306" t="s">
@@ -15740,7 +15747,7 @@
       <c r="B307" t="s">
         <v>1416</v>
       </c>
-      <c r="C307">
+      <c r="C307" s="11">
         <v>2011</v>
       </c>
       <c r="D307" t="s">
@@ -15776,7 +15783,7 @@
       <c r="B308" t="s">
         <v>620</v>
       </c>
-      <c r="C308">
+      <c r="C308" s="11">
         <v>2011</v>
       </c>
       <c r="D308" t="s">
@@ -15812,7 +15819,7 @@
       <c r="B309" t="s">
         <v>621</v>
       </c>
-      <c r="C309">
+      <c r="C309" s="11">
         <v>2011</v>
       </c>
       <c r="D309" t="s">
@@ -15836,7 +15843,7 @@
       <c r="B310" t="s">
         <v>622</v>
       </c>
-      <c r="C310">
+      <c r="C310" s="11">
         <v>2011</v>
       </c>
       <c r="D310" t="s">
@@ -15860,7 +15867,7 @@
       <c r="B311" t="s">
         <v>738</v>
       </c>
-      <c r="C311">
+      <c r="C311" s="11">
         <v>2011</v>
       </c>
       <c r="D311" t="s">
@@ -15892,7 +15899,7 @@
       <c r="B312" t="s">
         <v>623</v>
       </c>
-      <c r="C312">
+      <c r="C312" s="11">
         <v>2011</v>
       </c>
       <c r="D312" t="s">
@@ -15924,7 +15931,7 @@
       <c r="B313" t="s">
         <v>624</v>
       </c>
-      <c r="C313">
+      <c r="C313" s="11">
         <v>2011</v>
       </c>
       <c r="D313" t="s">
@@ -15948,7 +15955,7 @@
       <c r="B314" t="s">
         <v>625</v>
       </c>
-      <c r="C314">
+      <c r="C314" s="11">
         <v>2011</v>
       </c>
       <c r="D314" t="s">
@@ -15976,7 +15983,7 @@
       <c r="B315" t="s">
         <v>626</v>
       </c>
-      <c r="C315">
+      <c r="C315" s="11">
         <v>2011</v>
       </c>
       <c r="D315" t="s">
@@ -16008,7 +16015,7 @@
       <c r="B316" t="s">
         <v>474</v>
       </c>
-      <c r="C316">
+      <c r="C316" s="11">
         <v>2011</v>
       </c>
       <c r="D316" t="s">
@@ -16040,7 +16047,7 @@
       <c r="B317" t="s">
         <v>627</v>
       </c>
-      <c r="C317">
+      <c r="C317" s="11">
         <v>2011</v>
       </c>
       <c r="D317" t="s">
@@ -16076,7 +16083,7 @@
       <c r="B318" t="s">
         <v>627</v>
       </c>
-      <c r="C318">
+      <c r="C318" s="11">
         <v>2010</v>
       </c>
       <c r="D318" t="s">
@@ -16098,7 +16105,7 @@
       <c r="B319" t="s">
         <v>628</v>
       </c>
-      <c r="C319">
+      <c r="C319" s="11">
         <v>2010</v>
       </c>
       <c r="D319" t="s">
@@ -16134,7 +16141,7 @@
       <c r="B320" t="s">
         <v>629</v>
       </c>
-      <c r="C320">
+      <c r="C320" s="11">
         <v>2010</v>
       </c>
       <c r="D320" t="s">
@@ -16168,7 +16175,7 @@
       <c r="B321" t="s">
         <v>630</v>
       </c>
-      <c r="C321">
+      <c r="C321" s="11">
         <v>2010</v>
       </c>
       <c r="D321" t="s">
@@ -16198,7 +16205,7 @@
       <c r="B322" t="s">
         <v>721</v>
       </c>
-      <c r="C322">
+      <c r="C322" s="11">
         <v>2010</v>
       </c>
       <c r="D322" t="s">
@@ -16234,7 +16241,7 @@
       <c r="B323" t="s">
         <v>495</v>
       </c>
-      <c r="C323">
+      <c r="C323" s="11">
         <v>2010</v>
       </c>
       <c r="D323" t="s">
@@ -16270,7 +16277,7 @@
       <c r="B324" t="s">
         <v>731</v>
       </c>
-      <c r="C324">
+      <c r="C324" s="11">
         <v>2010</v>
       </c>
       <c r="D324" t="s">
@@ -16304,7 +16311,7 @@
       <c r="B325" t="s">
         <v>631</v>
       </c>
-      <c r="C325">
+      <c r="C325" s="11">
         <v>2010</v>
       </c>
       <c r="D325" t="s">
@@ -16338,7 +16345,7 @@
       <c r="B326" t="s">
         <v>632</v>
       </c>
-      <c r="C326">
+      <c r="C326" s="11">
         <v>2010</v>
       </c>
       <c r="D326" t="s">
@@ -16374,7 +16381,7 @@
       <c r="B327" t="s">
         <v>633</v>
       </c>
-      <c r="C327">
+      <c r="C327" s="11">
         <v>2010</v>
       </c>
       <c r="D327" t="s">
@@ -16410,7 +16417,7 @@
       <c r="B328" t="s">
         <v>634</v>
       </c>
-      <c r="C328">
+      <c r="C328" s="11">
         <v>2010</v>
       </c>
       <c r="D328" t="s">
@@ -16434,7 +16441,7 @@
       <c r="B329" t="s">
         <v>1709</v>
       </c>
-      <c r="C329">
+      <c r="C329" s="11">
         <v>2010</v>
       </c>
       <c r="D329" t="s">
@@ -16466,7 +16473,7 @@
       <c r="B330" t="s">
         <v>1457</v>
       </c>
-      <c r="C330">
+      <c r="C330" s="11">
         <v>2010</v>
       </c>
       <c r="D330" t="s">
@@ -16498,7 +16505,7 @@
       <c r="B331" t="s">
         <v>1727</v>
       </c>
-      <c r="C331">
+      <c r="C331" s="11">
         <v>2010</v>
       </c>
       <c r="D331" t="s">
@@ -16528,7 +16535,7 @@
       <c r="B332" t="s">
         <v>1710</v>
       </c>
-      <c r="C332">
+      <c r="C332" s="11">
         <v>2010</v>
       </c>
       <c r="D332" t="s">
@@ -16560,7 +16567,7 @@
       <c r="B333" t="s">
         <v>1692</v>
       </c>
-      <c r="C333">
+      <c r="C333" s="11">
         <v>2010</v>
       </c>
       <c r="D333" t="s">
@@ -16590,7 +16597,7 @@
       <c r="B334" t="s">
         <v>1694</v>
       </c>
-      <c r="C334">
+      <c r="C334" s="11">
         <v>2010</v>
       </c>
       <c r="D334" t="s">
@@ -16620,7 +16627,7 @@
       <c r="B335" t="s">
         <v>635</v>
       </c>
-      <c r="C335">
+      <c r="C335" s="11">
         <v>2010</v>
       </c>
       <c r="D335" t="s">
@@ -16644,7 +16651,7 @@
       <c r="B336" t="s">
         <v>1729</v>
       </c>
-      <c r="C336">
+      <c r="C336" s="11">
         <v>2010</v>
       </c>
       <c r="D336" t="s">
@@ -16672,7 +16679,7 @@
       <c r="B337" t="s">
         <v>636</v>
       </c>
-      <c r="C337">
+      <c r="C337" s="11">
         <v>2010</v>
       </c>
       <c r="D337" t="s">
@@ -16696,7 +16703,7 @@
       <c r="B338" t="s">
         <v>1722</v>
       </c>
-      <c r="C338">
+      <c r="C338" s="11">
         <v>2010</v>
       </c>
       <c r="D338" t="s">
@@ -16728,7 +16735,7 @@
       <c r="B339" t="s">
         <v>637</v>
       </c>
-      <c r="C339">
+      <c r="C339" s="11">
         <v>2010</v>
       </c>
       <c r="D339" t="s">
@@ -16752,7 +16759,7 @@
       <c r="B340" t="s">
         <v>627</v>
       </c>
-      <c r="C340">
+      <c r="C340" s="11">
         <v>2010</v>
       </c>
       <c r="D340" t="s">
@@ -16776,7 +16783,7 @@
       <c r="B341" t="s">
         <v>316</v>
       </c>
-      <c r="C341">
+      <c r="C341" s="11">
         <v>2009</v>
       </c>
       <c r="D341" t="s">
@@ -16800,7 +16807,7 @@
       <c r="B342" t="s">
         <v>1711</v>
       </c>
-      <c r="C342">
+      <c r="C342" s="11">
         <v>2009</v>
       </c>
       <c r="D342" t="s">
@@ -16836,7 +16843,7 @@
       <c r="B343" t="s">
         <v>1724</v>
       </c>
-      <c r="C343">
+      <c r="C343" s="11">
         <v>2009</v>
       </c>
       <c r="D343" t="s">
@@ -16868,7 +16875,7 @@
       <c r="B344" t="s">
         <v>1728</v>
       </c>
-      <c r="C344">
+      <c r="C344" s="11">
         <v>2009</v>
       </c>
       <c r="D344" t="s">
@@ -16904,7 +16911,7 @@
       <c r="B345" t="s">
         <v>495</v>
       </c>
-      <c r="C345">
+      <c r="C345" s="11">
         <v>2009</v>
       </c>
       <c r="D345" t="s">
@@ -16940,7 +16947,7 @@
       <c r="B346" t="s">
         <v>638</v>
       </c>
-      <c r="C346">
+      <c r="C346" s="11">
         <v>2009</v>
       </c>
       <c r="D346" t="s">
@@ -16964,7 +16971,7 @@
       <c r="B347" t="s">
         <v>639</v>
       </c>
-      <c r="C347">
+      <c r="C347" s="11">
         <v>2009</v>
       </c>
       <c r="D347" t="s">
@@ -16988,7 +16995,7 @@
       <c r="B348" t="s">
         <v>640</v>
       </c>
-      <c r="C348">
+      <c r="C348" s="11">
         <v>2009</v>
       </c>
       <c r="D348" t="s">
@@ -17012,7 +17019,7 @@
       <c r="B349" t="s">
         <v>641</v>
       </c>
-      <c r="C349">
+      <c r="C349" s="11">
         <v>2009</v>
       </c>
       <c r="D349" t="s">
@@ -17036,7 +17043,7 @@
       <c r="B350" t="s">
         <v>642</v>
       </c>
-      <c r="C350">
+      <c r="C350" s="11">
         <v>2009</v>
       </c>
       <c r="D350" t="s">
@@ -17064,7 +17071,7 @@
       <c r="B351" t="s">
         <v>1725</v>
       </c>
-      <c r="C351">
+      <c r="C351" s="11">
         <v>2009</v>
       </c>
       <c r="D351" t="s">
@@ -17096,7 +17103,7 @@
       <c r="B352" t="s">
         <v>643</v>
       </c>
-      <c r="C352">
+      <c r="C352" s="11">
         <v>2009</v>
       </c>
       <c r="D352" t="s">
@@ -17126,7 +17133,7 @@
       <c r="B353" t="s">
         <v>1490</v>
       </c>
-      <c r="C353">
+      <c r="C353" s="11">
         <v>2009</v>
       </c>
       <c r="D353" t="s">
@@ -17156,7 +17163,7 @@
       <c r="B354" t="s">
         <v>644</v>
       </c>
-      <c r="C354">
+      <c r="C354" s="11">
         <v>2009</v>
       </c>
       <c r="D354" t="s">
@@ -17188,7 +17195,7 @@
       <c r="B355" t="s">
         <v>732</v>
       </c>
-      <c r="C355">
+      <c r="C355" s="11">
         <v>2009</v>
       </c>
       <c r="D355" t="s">
@@ -17216,7 +17223,7 @@
       <c r="B356" t="s">
         <v>571</v>
       </c>
-      <c r="C356">
+      <c r="C356" s="11">
         <v>2008</v>
       </c>
       <c r="D356" t="s">
@@ -17252,7 +17259,7 @@
       <c r="B357" t="s">
         <v>645</v>
       </c>
-      <c r="C357">
+      <c r="C357" s="11">
         <v>2008</v>
       </c>
       <c r="D357" t="s">
@@ -17288,7 +17295,7 @@
       <c r="B358" t="s">
         <v>646</v>
       </c>
-      <c r="C358">
+      <c r="C358" s="11">
         <v>2008</v>
       </c>
       <c r="D358" t="s">
@@ -17312,7 +17319,7 @@
       <c r="B359" t="s">
         <v>647</v>
       </c>
-      <c r="C359">
+      <c r="C359" s="11">
         <v>2008</v>
       </c>
       <c r="D359" t="s">
@@ -17348,7 +17355,7 @@
       <c r="B360" t="s">
         <v>729</v>
       </c>
-      <c r="C360">
+      <c r="C360" s="11">
         <v>2008</v>
       </c>
       <c r="D360" t="s">
@@ -17382,7 +17389,7 @@
       <c r="B361" t="s">
         <v>316</v>
       </c>
-      <c r="C361">
+      <c r="C361" s="11">
         <v>2008</v>
       </c>
       <c r="D361" t="s">
@@ -17406,7 +17413,7 @@
       <c r="B362" t="s">
         <v>649</v>
       </c>
-      <c r="C362">
+      <c r="C362" s="11">
         <v>2008</v>
       </c>
       <c r="D362" t="s">
@@ -17438,7 +17445,7 @@
       <c r="B363" t="s">
         <v>633</v>
       </c>
-      <c r="C363">
+      <c r="C363" s="11">
         <v>2008</v>
       </c>
       <c r="D363" t="s">
@@ -17466,7 +17473,7 @@
       <c r="B364" t="s">
         <v>1519</v>
       </c>
-      <c r="C364">
+      <c r="C364" s="11">
         <v>2008</v>
       </c>
       <c r="D364" t="s">
@@ -17494,7 +17501,7 @@
       <c r="B365" t="s">
         <v>650</v>
       </c>
-      <c r="C365">
+      <c r="C365" s="11">
         <v>2008</v>
       </c>
       <c r="D365" t="s">
@@ -17518,7 +17525,7 @@
       <c r="B366" t="s">
         <v>651</v>
       </c>
-      <c r="C366">
+      <c r="C366" s="11">
         <v>2008</v>
       </c>
       <c r="D366" t="s">
@@ -17546,7 +17553,7 @@
       <c r="B367" t="s">
         <v>652</v>
       </c>
-      <c r="C367">
+      <c r="C367" s="11">
         <v>2008</v>
       </c>
       <c r="D367" t="s">
@@ -17578,7 +17585,7 @@
       <c r="B368" t="s">
         <v>653</v>
       </c>
-      <c r="C368">
+      <c r="C368" s="11">
         <v>2008</v>
       </c>
       <c r="D368" t="s">
@@ -17606,7 +17613,7 @@
       <c r="B369" t="s">
         <v>654</v>
       </c>
-      <c r="C369">
+      <c r="C369" s="11">
         <v>2008</v>
       </c>
       <c r="D369" t="s">
@@ -17634,7 +17641,7 @@
       <c r="B370" t="s">
         <v>655</v>
       </c>
-      <c r="C370">
+      <c r="C370" s="11">
         <v>2008</v>
       </c>
       <c r="D370" t="s">
@@ -17662,7 +17669,7 @@
       <c r="B371" t="s">
         <v>740</v>
       </c>
-      <c r="C371">
+      <c r="C371" s="11">
         <v>2008</v>
       </c>
       <c r="D371" t="s">
@@ -17690,7 +17697,7 @@
       <c r="B372" t="s">
         <v>656</v>
       </c>
-      <c r="C372">
+      <c r="C372" s="11">
         <v>2008</v>
       </c>
       <c r="D372" t="s">
@@ -17712,7 +17719,7 @@
       <c r="B373" t="s">
         <v>657</v>
       </c>
-      <c r="C373">
+      <c r="C373" s="11">
         <v>2008</v>
       </c>
       <c r="D373" t="s">
@@ -17740,7 +17747,7 @@
       <c r="B374" t="s">
         <v>657</v>
       </c>
-      <c r="C374">
+      <c r="C374" s="11">
         <v>2008</v>
       </c>
       <c r="D374" t="s">
@@ -17764,7 +17771,7 @@
       <c r="B375" t="s">
         <v>658</v>
       </c>
-      <c r="C375">
+      <c r="C375" s="11">
         <v>2008</v>
       </c>
       <c r="D375" t="s">
@@ -17800,7 +17807,7 @@
       <c r="B376" t="s">
         <v>659</v>
       </c>
-      <c r="C376">
+      <c r="C376" s="11">
         <v>2008</v>
       </c>
       <c r="D376" t="s">
@@ -17828,7 +17835,7 @@
       <c r="B377" t="s">
         <v>477</v>
       </c>
-      <c r="C377">
+      <c r="C377" s="11">
         <v>2008</v>
       </c>
       <c r="D377" t="s">
@@ -17860,7 +17867,7 @@
       <c r="B378" t="s">
         <v>1548</v>
       </c>
-      <c r="C378">
+      <c r="C378" s="11">
         <v>2008</v>
       </c>
       <c r="D378" t="s">
@@ -17888,7 +17895,7 @@
       <c r="B379" t="s">
         <v>478</v>
       </c>
-      <c r="C379">
+      <c r="C379" s="11">
         <v>2008</v>
       </c>
       <c r="D379" t="s">
@@ -17910,7 +17917,7 @@
       <c r="B380" t="s">
         <v>479</v>
       </c>
-      <c r="C380">
+      <c r="C380" s="11">
         <v>2008</v>
       </c>
       <c r="D380" t="s">
@@ -17932,7 +17939,7 @@
       <c r="B381" t="s">
         <v>648</v>
       </c>
-      <c r="C381">
+      <c r="C381" s="11">
         <v>2007</v>
       </c>
       <c r="D381" t="s">
@@ -17968,7 +17975,7 @@
       <c r="B382" t="s">
         <v>660</v>
       </c>
-      <c r="C382">
+      <c r="C382" s="11">
         <v>2007</v>
       </c>
       <c r="D382" t="s">
@@ -17996,7 +18003,7 @@
       <c r="B383" t="s">
         <v>495</v>
       </c>
-      <c r="C383">
+      <c r="C383" s="11">
         <v>2007</v>
       </c>
       <c r="D383" t="s">
@@ -18032,7 +18039,7 @@
       <c r="B384" t="s">
         <v>661</v>
       </c>
-      <c r="C384">
+      <c r="C384" s="11">
         <v>2007</v>
       </c>
       <c r="D384" t="s">
@@ -18068,7 +18075,7 @@
       <c r="B385" t="s">
         <v>663</v>
       </c>
-      <c r="C385">
+      <c r="C385" s="11">
         <v>2007</v>
       </c>
       <c r="D385" t="s">
@@ -18092,7 +18099,7 @@
       <c r="B386" t="s">
         <v>664</v>
       </c>
-      <c r="C386">
+      <c r="C386" s="11">
         <v>2007</v>
       </c>
       <c r="D386" t="s">
@@ -18114,7 +18121,7 @@
       <c r="B387" t="s">
         <v>477</v>
       </c>
-      <c r="C387">
+      <c r="C387" s="11">
         <v>2007</v>
       </c>
       <c r="D387" t="s">
@@ -18146,7 +18153,7 @@
       <c r="B388" t="s">
         <v>665</v>
       </c>
-      <c r="C388">
+      <c r="C388" s="11">
         <v>2007</v>
       </c>
       <c r="D388" t="s">
@@ -18170,7 +18177,7 @@
       <c r="B389" t="s">
         <v>666</v>
       </c>
-      <c r="C389">
+      <c r="C389" s="11">
         <v>2007</v>
       </c>
       <c r="D389" t="s">
@@ -18202,7 +18209,7 @@
       <c r="B390" t="s">
         <v>667</v>
       </c>
-      <c r="C390">
+      <c r="C390" s="11">
         <v>2007</v>
       </c>
       <c r="D390" t="s">
@@ -18238,7 +18245,7 @@
       <c r="B391" t="s">
         <v>1566</v>
       </c>
-      <c r="C391">
+      <c r="C391" s="11">
         <v>2007</v>
       </c>
       <c r="D391" t="s">
@@ -18270,7 +18277,7 @@
       <c r="B392" t="s">
         <v>477</v>
       </c>
-      <c r="C392">
+      <c r="C392" s="11">
         <v>2007</v>
       </c>
       <c r="D392" t="s">
@@ -18302,7 +18309,7 @@
       <c r="B393" t="s">
         <v>668</v>
       </c>
-      <c r="C393">
+      <c r="C393" s="11">
         <v>2007</v>
       </c>
       <c r="D393" t="s">
@@ -18330,7 +18337,7 @@
       <c r="B394" t="s">
         <v>669</v>
       </c>
-      <c r="C394">
+      <c r="C394" s="11">
         <v>2007</v>
       </c>
       <c r="D394" t="s">
@@ -18358,7 +18365,7 @@
       <c r="B395" t="s">
         <v>670</v>
       </c>
-      <c r="C395">
+      <c r="C395" s="11">
         <v>2007</v>
       </c>
       <c r="D395" t="s">
@@ -18390,7 +18397,7 @@
       <c r="B396" t="s">
         <v>671</v>
       </c>
-      <c r="C396">
+      <c r="C396" s="11">
         <v>2007</v>
       </c>
       <c r="D396" t="s">
@@ -18418,7 +18425,7 @@
       <c r="B397" t="s">
         <v>661</v>
       </c>
-      <c r="C397">
+      <c r="C397" s="11">
         <v>2007</v>
       </c>
       <c r="D397" t="s">
@@ -18446,7 +18453,7 @@
       <c r="B398" t="s">
         <v>633</v>
       </c>
-      <c r="C398">
+      <c r="C398" s="11">
         <v>2007</v>
       </c>
       <c r="D398" t="s">
@@ -18478,7 +18485,7 @@
       <c r="B399" t="s">
         <v>633</v>
       </c>
-      <c r="C399">
+      <c r="C399" s="11">
         <v>2007</v>
       </c>
       <c r="D399" t="s">
@@ -18510,7 +18517,7 @@
       <c r="B400" t="s">
         <v>733</v>
       </c>
-      <c r="C400">
+      <c r="C400" s="11">
         <v>2007</v>
       </c>
       <c r="D400" t="s">
@@ -18534,7 +18541,7 @@
       <c r="B401" t="s">
         <v>739</v>
       </c>
-      <c r="C401">
+      <c r="C401" s="11">
         <v>2007</v>
       </c>
       <c r="D401" t="s">
@@ -18566,7 +18573,7 @@
       <c r="B402" t="s">
         <v>661</v>
       </c>
-      <c r="C402">
+      <c r="C402" s="11">
         <v>2007</v>
       </c>
       <c r="D402" t="s">
@@ -18590,7 +18597,7 @@
       <c r="B403" t="s">
         <v>363</v>
       </c>
-      <c r="C403">
+      <c r="C403" s="11">
         <v>2007</v>
       </c>
       <c r="D403" t="s">
@@ -18618,7 +18625,7 @@
       <c r="B404" t="s">
         <v>480</v>
       </c>
-      <c r="C404">
+      <c r="C404" s="11">
         <v>2007</v>
       </c>
       <c r="D404" t="s">
@@ -18642,7 +18649,7 @@
       <c r="B405" t="s">
         <v>719</v>
       </c>
-      <c r="C405">
+      <c r="C405" s="11">
         <v>2007</v>
       </c>
       <c r="D405" t="s">
@@ -18664,7 +18671,7 @@
       <c r="B406" t="s">
         <v>720</v>
       </c>
-      <c r="C406">
+      <c r="C406" s="11">
         <v>2007</v>
       </c>
       <c r="D406" t="s">
@@ -18688,7 +18695,7 @@
       <c r="B407" t="s">
         <v>672</v>
       </c>
-      <c r="C407">
+      <c r="C407" s="11">
         <v>2007</v>
       </c>
       <c r="D407" t="s">
@@ -18712,7 +18719,7 @@
       <c r="B408" t="s">
         <v>673</v>
       </c>
-      <c r="C408">
+      <c r="C408" s="11">
         <v>2007</v>
       </c>
       <c r="D408" t="s">
@@ -18744,7 +18751,7 @@
       <c r="B409" t="s">
         <v>673</v>
       </c>
-      <c r="C409">
+      <c r="C409" s="11">
         <v>2007</v>
       </c>
       <c r="D409" t="s">
@@ -18776,7 +18783,7 @@
       <c r="B410" t="s">
         <v>674</v>
       </c>
-      <c r="C410">
+      <c r="C410" s="11">
         <v>2007</v>
       </c>
       <c r="D410" t="s">
@@ -18798,7 +18805,7 @@
       <c r="B411" t="s">
         <v>662</v>
       </c>
-      <c r="C411">
+      <c r="C411" s="11">
         <v>2006</v>
       </c>
       <c r="D411" t="s">
@@ -18834,7 +18841,7 @@
       <c r="B412" t="s">
         <v>1595</v>
       </c>
-      <c r="C412">
+      <c r="C412" s="11">
         <v>2006</v>
       </c>
       <c r="D412" t="s">
@@ -18866,7 +18873,7 @@
       <c r="B413" t="s">
         <v>675</v>
       </c>
-      <c r="C413">
+      <c r="C413" s="11">
         <v>2006</v>
       </c>
       <c r="D413" t="s">
@@ -18890,7 +18897,7 @@
       <c r="B414" t="s">
         <v>676</v>
       </c>
-      <c r="C414">
+      <c r="C414" s="11">
         <v>2006</v>
       </c>
       <c r="D414" t="s">
@@ -18926,7 +18933,7 @@
       <c r="B415" t="s">
         <v>677</v>
       </c>
-      <c r="C415">
+      <c r="C415" s="11">
         <v>2006</v>
       </c>
       <c r="D415" t="s">
@@ -18958,7 +18965,7 @@
       <c r="B416" t="s">
         <v>1604</v>
       </c>
-      <c r="C416">
+      <c r="C416" s="11">
         <v>2006</v>
       </c>
       <c r="D416" t="s">
@@ -18994,7 +19001,7 @@
       <c r="B417" t="s">
         <v>734</v>
       </c>
-      <c r="C417">
+      <c r="C417" s="11">
         <v>2006</v>
       </c>
       <c r="D417" t="s">
@@ -19018,7 +19025,7 @@
       <c r="B418" t="s">
         <v>662</v>
       </c>
-      <c r="C418">
+      <c r="C418" s="11">
         <v>2006</v>
       </c>
       <c r="D418" t="s">
@@ -19054,7 +19061,7 @@
       <c r="B419" t="s">
         <v>678</v>
       </c>
-      <c r="C419">
+      <c r="C419" s="11">
         <v>2006</v>
       </c>
       <c r="D419" t="s">
@@ -19078,7 +19085,7 @@
       <c r="B420" t="s">
         <v>679</v>
       </c>
-      <c r="C420">
+      <c r="C420" s="11">
         <v>2006</v>
       </c>
       <c r="D420" t="s">
@@ -19102,7 +19109,7 @@
       <c r="B421" t="s">
         <v>1610</v>
       </c>
-      <c r="C421">
+      <c r="C421" s="11">
         <v>2006</v>
       </c>
       <c r="D421" t="s">
@@ -19134,7 +19141,7 @@
       <c r="B422" t="s">
         <v>1613</v>
       </c>
-      <c r="C422">
+      <c r="C422" s="11">
         <v>2006</v>
       </c>
       <c r="D422" t="s">
@@ -19162,7 +19169,7 @@
       <c r="B423" t="s">
         <v>675</v>
       </c>
-      <c r="C423">
+      <c r="C423" s="11">
         <v>2006</v>
       </c>
       <c r="D423" t="s">
@@ -19186,7 +19193,7 @@
       <c r="B424" t="s">
         <v>680</v>
       </c>
-      <c r="C424">
+      <c r="C424" s="11">
         <v>2006</v>
       </c>
       <c r="D424" t="s">
@@ -19210,7 +19217,7 @@
       <c r="B425" t="s">
         <v>653</v>
       </c>
-      <c r="C425">
+      <c r="C425" s="11">
         <v>2006</v>
       </c>
       <c r="D425" t="s">
@@ -19234,7 +19241,7 @@
       <c r="B426" t="s">
         <v>681</v>
       </c>
-      <c r="C426">
+      <c r="C426" s="11">
         <v>2006</v>
       </c>
       <c r="D426" t="s">
@@ -19258,7 +19265,7 @@
       <c r="B427" t="s">
         <v>682</v>
       </c>
-      <c r="C427">
+      <c r="C427" s="11">
         <v>2006</v>
       </c>
       <c r="D427" t="s">
@@ -19290,7 +19297,7 @@
       <c r="B428" t="s">
         <v>683</v>
       </c>
-      <c r="C428">
+      <c r="C428" s="11">
         <v>2006</v>
       </c>
       <c r="D428" t="s">
@@ -19314,7 +19321,7 @@
       <c r="B429" t="s">
         <v>684</v>
       </c>
-      <c r="C429">
+      <c r="C429" s="11">
         <v>2006</v>
       </c>
       <c r="D429" t="s">
@@ -19338,7 +19345,7 @@
       <c r="B430" t="s">
         <v>685</v>
       </c>
-      <c r="C430">
+      <c r="C430" s="11">
         <v>2006</v>
       </c>
       <c r="D430" t="s">
@@ -19362,7 +19369,7 @@
       <c r="B431" t="s">
         <v>686</v>
       </c>
-      <c r="C431">
+      <c r="C431" s="11">
         <v>2006</v>
       </c>
       <c r="D431" t="s">
@@ -19394,7 +19401,7 @@
       <c r="B432" t="s">
         <v>686</v>
       </c>
-      <c r="C432">
+      <c r="C432" s="11">
         <v>2006</v>
       </c>
       <c r="D432" t="s">
@@ -19426,7 +19433,7 @@
       <c r="B433" t="s">
         <v>687</v>
       </c>
-      <c r="C433">
+      <c r="C433" s="11">
         <v>2006</v>
       </c>
       <c r="D433" t="s">
@@ -19458,7 +19465,7 @@
       <c r="B434" t="s">
         <v>688</v>
       </c>
-      <c r="C434">
+      <c r="C434" s="11">
         <v>2006</v>
       </c>
       <c r="D434" t="s">
@@ -19482,7 +19489,7 @@
       <c r="B435" t="s">
         <v>689</v>
       </c>
-      <c r="C435">
+      <c r="C435" s="11">
         <v>2006</v>
       </c>
       <c r="D435" t="s">
@@ -19506,7 +19513,7 @@
       <c r="B436" t="s">
         <v>690</v>
       </c>
-      <c r="C436">
+      <c r="C436" s="11">
         <v>2006</v>
       </c>
       <c r="D436" t="s">
@@ -19530,7 +19537,7 @@
       <c r="B437" t="s">
         <v>571</v>
       </c>
-      <c r="C437">
+      <c r="C437" s="11">
         <v>2005</v>
       </c>
       <c r="D437" t="s">
@@ -19566,7 +19573,7 @@
       <c r="B438" t="s">
         <v>691</v>
       </c>
-      <c r="C438">
+      <c r="C438" s="11">
         <v>2005</v>
       </c>
       <c r="D438" t="s">
@@ -19600,7 +19607,7 @@
       <c r="B439" t="s">
         <v>662</v>
       </c>
-      <c r="C439">
+      <c r="C439" s="11">
         <v>2005</v>
       </c>
       <c r="D439" t="s">
@@ -19636,7 +19643,7 @@
       <c r="B440" t="s">
         <v>692</v>
       </c>
-      <c r="C440">
+      <c r="C440" s="11">
         <v>2005</v>
       </c>
       <c r="D440" t="s">
@@ -19672,7 +19679,7 @@
       <c r="B441" t="s">
         <v>692</v>
       </c>
-      <c r="C441">
+      <c r="C441" s="11">
         <v>2005</v>
       </c>
       <c r="D441" t="s">
@@ -19708,7 +19715,7 @@
       <c r="B442" t="s">
         <v>693</v>
       </c>
-      <c r="C442">
+      <c r="C442" s="11">
         <v>2005</v>
       </c>
       <c r="D442" t="s">
@@ -19736,7 +19743,7 @@
       <c r="B443" t="s">
         <v>495</v>
       </c>
-      <c r="C443">
+      <c r="C443" s="11">
         <v>2005</v>
       </c>
       <c r="D443" t="s">
@@ -19764,7 +19771,7 @@
       <c r="B444" t="s">
         <v>694</v>
       </c>
-      <c r="C444">
+      <c r="C444" s="11">
         <v>2005</v>
       </c>
       <c r="D444" t="s">
@@ -19792,7 +19799,7 @@
       <c r="B445" t="s">
         <v>695</v>
       </c>
-      <c r="C445">
+      <c r="C445" s="11">
         <v>2005</v>
       </c>
       <c r="D445" t="s">
@@ -19820,7 +19827,7 @@
       <c r="B446" t="s">
         <v>676</v>
       </c>
-      <c r="C446">
+      <c r="C446" s="11">
         <v>2005</v>
       </c>
       <c r="D446" t="s">
@@ -19844,7 +19851,7 @@
       <c r="B447" t="s">
         <v>696</v>
       </c>
-      <c r="C447">
+      <c r="C447" s="11">
         <v>2005</v>
       </c>
       <c r="D447" t="s">
@@ -19872,7 +19879,7 @@
       <c r="B448" t="s">
         <v>696</v>
       </c>
-      <c r="C448">
+      <c r="C448" s="11">
         <v>2005</v>
       </c>
       <c r="D448" t="s">
@@ -19896,7 +19903,7 @@
       <c r="B449" t="s">
         <v>697</v>
       </c>
-      <c r="C449">
+      <c r="C449" s="11">
         <v>2005</v>
       </c>
       <c r="D449" t="s">
@@ -19920,7 +19927,7 @@
       <c r="B450" t="s">
         <v>698</v>
       </c>
-      <c r="C450">
+      <c r="C450" s="11">
         <v>2005</v>
       </c>
       <c r="D450" t="s">
@@ -19944,7 +19951,7 @@
       <c r="B451" t="s">
         <v>699</v>
       </c>
-      <c r="C451">
+      <c r="C451" s="11">
         <v>2005</v>
       </c>
       <c r="D451" t="s">
@@ -19968,7 +19975,7 @@
       <c r="B452" t="s">
         <v>722</v>
       </c>
-      <c r="C452">
+      <c r="C452" s="11">
         <v>2004</v>
       </c>
       <c r="D452" t="s">
@@ -20004,7 +20011,7 @@
       <c r="B453" t="s">
         <v>495</v>
       </c>
-      <c r="C453">
+      <c r="C453" s="11">
         <v>2004</v>
       </c>
       <c r="D453" t="s">
@@ -20040,7 +20047,7 @@
       <c r="B454" t="s">
         <v>700</v>
       </c>
-      <c r="C454">
+      <c r="C454" s="11">
         <v>2004</v>
       </c>
       <c r="D454" t="s">
@@ -20076,7 +20083,7 @@
       <c r="B455" t="s">
         <v>676</v>
       </c>
-      <c r="C455">
+      <c r="C455" s="11">
         <v>2004</v>
       </c>
       <c r="D455" t="s">
@@ -20112,7 +20119,7 @@
       <c r="B456" t="s">
         <v>695</v>
       </c>
-      <c r="C456">
+      <c r="C456" s="11">
         <v>2004</v>
       </c>
       <c r="D456" t="s">
@@ -20140,7 +20147,7 @@
       <c r="B457" t="s">
         <v>677</v>
       </c>
-      <c r="C457">
+      <c r="C457" s="11">
         <v>2004</v>
       </c>
       <c r="D457" t="s">
@@ -20168,7 +20175,7 @@
       <c r="B458" t="s">
         <v>676</v>
       </c>
-      <c r="C458">
+      <c r="C458" s="11">
         <v>2004</v>
       </c>
       <c r="D458" t="s">
@@ -20192,7 +20199,7 @@
       <c r="B459" t="s">
         <v>695</v>
       </c>
-      <c r="C459">
+      <c r="C459" s="11">
         <v>2004</v>
       </c>
       <c r="D459" t="s">
@@ -20220,7 +20227,7 @@
       <c r="B460" t="s">
         <v>701</v>
       </c>
-      <c r="C460">
+      <c r="C460" s="11">
         <v>2004</v>
       </c>
       <c r="D460" t="s">
@@ -20244,7 +20251,7 @@
       <c r="B461" t="s">
         <v>702</v>
       </c>
-      <c r="C461">
+      <c r="C461" s="11">
         <v>2004</v>
       </c>
       <c r="D461" t="s">
@@ -20268,7 +20275,7 @@
       <c r="B462" t="s">
         <v>698</v>
       </c>
-      <c r="C462">
+      <c r="C462" s="11">
         <v>2004</v>
       </c>
       <c r="D462" t="s">
@@ -20292,7 +20299,7 @@
       <c r="B463" t="s">
         <v>703</v>
       </c>
-      <c r="C463">
+      <c r="C463" s="11">
         <v>2004</v>
       </c>
       <c r="D463" t="s">
@@ -20316,7 +20323,7 @@
       <c r="B464" t="s">
         <v>704</v>
       </c>
-      <c r="C464">
+      <c r="C464" s="11">
         <v>2004</v>
       </c>
       <c r="D464" t="s">
@@ -20340,7 +20347,7 @@
       <c r="B465" t="s">
         <v>705</v>
       </c>
-      <c r="C465">
+      <c r="C465" s="11">
         <v>2004</v>
       </c>
       <c r="D465" t="s">
@@ -20368,7 +20375,7 @@
       <c r="B466" t="s">
         <v>706</v>
       </c>
-      <c r="C466">
+      <c r="C466" s="11">
         <v>2003</v>
       </c>
       <c r="D466" t="s">
@@ -20392,7 +20399,7 @@
       <c r="B467" t="s">
         <v>707</v>
       </c>
-      <c r="C467">
+      <c r="C467" s="11">
         <v>2003</v>
       </c>
       <c r="D467" t="s">
@@ -20428,7 +20435,7 @@
       <c r="B468" t="s">
         <v>708</v>
       </c>
-      <c r="C468">
+      <c r="C468" s="11">
         <v>2003</v>
       </c>
       <c r="D468" t="s">
@@ -20452,7 +20459,7 @@
       <c r="B469" t="s">
         <v>722</v>
       </c>
-      <c r="C469">
+      <c r="C469" s="11">
         <v>2003</v>
       </c>
       <c r="D469" t="s">
@@ -20488,7 +20495,7 @@
       <c r="B470" t="s">
         <v>709</v>
       </c>
-      <c r="C470">
+      <c r="C470" s="11">
         <v>2003</v>
       </c>
       <c r="D470" t="s">
@@ -20512,7 +20519,7 @@
       <c r="B471" t="s">
         <v>698</v>
       </c>
-      <c r="C471">
+      <c r="C471" s="11">
         <v>2003</v>
       </c>
       <c r="D471" t="s">
@@ -20536,7 +20543,7 @@
       <c r="B472" t="s">
         <v>692</v>
       </c>
-      <c r="C472">
+      <c r="C472" s="11">
         <v>2003</v>
       </c>
       <c r="D472" t="s">
@@ -20564,7 +20571,7 @@
       <c r="B473" t="s">
         <v>692</v>
       </c>
-      <c r="C473">
+      <c r="C473" s="11">
         <v>2003</v>
       </c>
       <c r="D473" t="s">
@@ -20592,7 +20599,7 @@
       <c r="B474" t="s">
         <v>676</v>
       </c>
-      <c r="C474">
+      <c r="C474" s="11">
         <v>2003</v>
       </c>
       <c r="D474" t="s">
@@ -20620,7 +20627,7 @@
       <c r="B475" t="s">
         <v>692</v>
       </c>
-      <c r="C475">
+      <c r="C475" s="11">
         <v>2002</v>
       </c>
       <c r="D475" t="s">
@@ -20656,7 +20663,7 @@
       <c r="B476" t="s">
         <v>700</v>
       </c>
-      <c r="C476">
+      <c r="C476" s="11">
         <v>2002</v>
       </c>
       <c r="D476" t="s">
@@ -20692,7 +20699,7 @@
       <c r="B477" t="s">
         <v>662</v>
       </c>
-      <c r="C477">
+      <c r="C477" s="11">
         <v>2002</v>
       </c>
       <c r="D477" t="s">
@@ -20726,7 +20733,7 @@
       <c r="B478" t="s">
         <v>662</v>
       </c>
-      <c r="C478">
+      <c r="C478" s="11">
         <v>2002</v>
       </c>
       <c r="D478" t="s">
@@ -20762,7 +20769,7 @@
       <c r="B479" t="s">
         <v>710</v>
       </c>
-      <c r="C479">
+      <c r="C479" s="11">
         <v>2002</v>
       </c>
       <c r="D479" t="s">
@@ -20786,7 +20793,7 @@
       <c r="B480" t="s">
         <v>711</v>
       </c>
-      <c r="C480">
+      <c r="C480" s="11">
         <v>2002</v>
       </c>
       <c r="D480" t="s">
@@ -20814,7 +20821,7 @@
       <c r="B481" t="s">
         <v>676</v>
       </c>
-      <c r="C481">
+      <c r="C481" s="11">
         <v>2002</v>
       </c>
       <c r="D481" t="s">
@@ -20838,7 +20845,7 @@
       <c r="B482" t="s">
         <v>712</v>
       </c>
-      <c r="C482">
+      <c r="C482" s="11">
         <v>2002</v>
       </c>
       <c r="D482" t="s">
@@ -20862,7 +20869,7 @@
       <c r="B483" t="s">
         <v>713</v>
       </c>
-      <c r="C483">
+      <c r="C483" s="11">
         <v>2002</v>
       </c>
       <c r="D483" t="s">
@@ -20890,7 +20897,7 @@
       <c r="B484" t="s">
         <v>662</v>
       </c>
-      <c r="C484">
+      <c r="C484" s="11">
         <v>2001</v>
       </c>
       <c r="D484" t="s">
@@ -20926,7 +20933,7 @@
       <c r="B485" t="s">
         <v>714</v>
       </c>
-      <c r="C485">
+      <c r="C485" s="11">
         <v>2001</v>
       </c>
       <c r="D485" t="s">
@@ -20962,7 +20969,7 @@
       <c r="B486" t="s">
         <v>715</v>
       </c>
-      <c r="C486">
+      <c r="C486" s="11">
         <v>2001</v>
       </c>
       <c r="D486" t="s">
@@ -20984,7 +20991,7 @@
       <c r="B487" t="s">
         <v>692</v>
       </c>
-      <c r="C487">
+      <c r="C487" s="11">
         <v>2001</v>
       </c>
       <c r="D487" t="s">
@@ -21012,7 +21019,7 @@
       <c r="B488" t="s">
         <v>716</v>
       </c>
-      <c r="C488">
+      <c r="C488" s="11">
         <v>2001</v>
       </c>
       <c r="D488" t="s">
@@ -21036,7 +21043,7 @@
       <c r="B489" t="s">
         <v>717</v>
       </c>
-      <c r="C489">
+      <c r="C489" s="11">
         <v>2001</v>
       </c>
       <c r="D489" t="s">
